--- a/Schema/xlsx/Sign.xlsx
+++ b/Schema/xlsx/Sign.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Users\peggy\Github\databaseproject-G9\Schema\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Users\peggy\Github\databaseproject-G9\Schema\xlsx\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C91E1265-F338-4319-8236-267ADECD58ED}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F1A41DA4-00D1-42D8-94EC-7C5D0E4DD496}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12645" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -100,7 +100,40 @@
   <cellStyles count="1">
     <cellStyle name="一般" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="2">
+  <dxfs count="7">
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFFF0000"/>
+      </font>
+    </dxf>
     <dxf>
       <border outline="0">
         <bottom style="dashed">
@@ -141,11 +174,11 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{DD8F713E-107F-4110-B8CB-4951C1ABB0D5}" name="表格1" displayName="表格1" ref="A1:B549" totalsRowShown="0" headerRowDxfId="1" headerRowBorderDxfId="0">
-  <autoFilter ref="A1:B549" xr:uid="{771B2A03-D511-4343-9332-8D746A5CAE61}"/>
-  <sortState ref="A2:B549">
-    <sortCondition ref="A2:A549"/>
-    <sortCondition ref="B2:B549"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{DD8F713E-107F-4110-B8CB-4951C1ABB0D5}" name="表格1" displayName="表格1" ref="A1:B575" totalsRowShown="0" headerRowDxfId="6" headerRowBorderDxfId="5">
+  <autoFilter ref="A1:B575" xr:uid="{771B2A03-D511-4343-9332-8D746A5CAE61}"/>
+  <sortState ref="A2:B575">
+    <sortCondition ref="A2:A575"/>
+    <sortCondition ref="B2:B575"/>
   </sortState>
   <tableColumns count="2">
     <tableColumn id="1" xr3:uid="{8519C55D-3A98-40DF-9E6B-81815082CFEB}" name="pIndex"/>
@@ -418,7 +451,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B549"/>
+  <dimension ref="A1:B575"/>
   <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
@@ -447,10 +480,10 @@
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B4">
-        <v>60</v>
+        <v>448</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
@@ -458,7 +491,7 @@
         <v>2</v>
       </c>
       <c r="B5">
-        <v>120</v>
+        <v>48</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
@@ -466,7 +499,7 @@
         <v>2</v>
       </c>
       <c r="B6">
-        <v>304</v>
+        <v>58</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
@@ -474,7 +507,7 @@
         <v>2</v>
       </c>
       <c r="B7">
-        <v>423</v>
+        <v>60</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
@@ -482,55 +515,55 @@
         <v>2</v>
       </c>
       <c r="B8">
-        <v>520</v>
+        <v>91</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B9">
-        <v>101</v>
+        <v>120</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B10">
-        <v>136</v>
+        <v>304</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B11">
-        <v>168</v>
+        <v>336</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B12">
-        <v>189</v>
+        <v>383</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B13">
-        <v>207</v>
+        <v>423</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B14">
-        <v>321</v>
+        <v>520</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.25">
@@ -538,7 +571,7 @@
         <v>3</v>
       </c>
       <c r="B15">
-        <v>347</v>
+        <v>101</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.25">
@@ -546,7 +579,7 @@
         <v>3</v>
       </c>
       <c r="B16">
-        <v>383</v>
+        <v>136</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.25">
@@ -554,87 +587,87 @@
         <v>3</v>
       </c>
       <c r="B17">
-        <v>421</v>
+        <v>145</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A18">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B18">
-        <v>1</v>
+        <v>168</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A19">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B19">
-        <v>22</v>
+        <v>189</v>
       </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A20">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B20">
-        <v>31</v>
+        <v>207</v>
       </c>
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A21">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B21">
-        <v>33</v>
+        <v>314</v>
       </c>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A22">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B22">
-        <v>34</v>
+        <v>321</v>
       </c>
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A23">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B23">
-        <v>35</v>
+        <v>347</v>
       </c>
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A24">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B24">
-        <v>37</v>
+        <v>383</v>
       </c>
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A25">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B25">
-        <v>38</v>
+        <v>421</v>
       </c>
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A26">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B26">
-        <v>39</v>
+        <v>441</v>
       </c>
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A27">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B27">
-        <v>40</v>
+        <v>548</v>
       </c>
     </row>
     <row r="28" spans="1:2" x14ac:dyDescent="0.25">
@@ -642,7 +675,7 @@
         <v>4</v>
       </c>
       <c r="B28">
-        <v>42</v>
+        <v>1</v>
       </c>
     </row>
     <row r="29" spans="1:2" x14ac:dyDescent="0.25">
@@ -650,7 +683,7 @@
         <v>4</v>
       </c>
       <c r="B29">
-        <v>45</v>
+        <v>22</v>
       </c>
     </row>
     <row r="30" spans="1:2" x14ac:dyDescent="0.25">
@@ -658,7 +691,7 @@
         <v>4</v>
       </c>
       <c r="B30">
-        <v>49</v>
+        <v>31</v>
       </c>
     </row>
     <row r="31" spans="1:2" x14ac:dyDescent="0.25">
@@ -666,7 +699,7 @@
         <v>4</v>
       </c>
       <c r="B31">
-        <v>51</v>
+        <v>33</v>
       </c>
     </row>
     <row r="32" spans="1:2" x14ac:dyDescent="0.25">
@@ -674,7 +707,7 @@
         <v>4</v>
       </c>
       <c r="B32">
-        <v>52</v>
+        <v>34</v>
       </c>
     </row>
     <row r="33" spans="1:2" x14ac:dyDescent="0.25">
@@ -682,7 +715,7 @@
         <v>4</v>
       </c>
       <c r="B33">
-        <v>56</v>
+        <v>35</v>
       </c>
     </row>
     <row r="34" spans="1:2" x14ac:dyDescent="0.25">
@@ -690,7 +723,7 @@
         <v>4</v>
       </c>
       <c r="B34">
-        <v>57</v>
+        <v>37</v>
       </c>
     </row>
     <row r="35" spans="1:2" x14ac:dyDescent="0.25">
@@ -698,7 +731,7 @@
         <v>4</v>
       </c>
       <c r="B35">
-        <v>61</v>
+        <v>38</v>
       </c>
     </row>
     <row r="36" spans="1:2" x14ac:dyDescent="0.25">
@@ -706,7 +739,7 @@
         <v>4</v>
       </c>
       <c r="B36">
-        <v>62</v>
+        <v>39</v>
       </c>
     </row>
     <row r="37" spans="1:2" x14ac:dyDescent="0.25">
@@ -714,7 +747,7 @@
         <v>4</v>
       </c>
       <c r="B37">
-        <v>63</v>
+        <v>40</v>
       </c>
     </row>
     <row r="38" spans="1:2" x14ac:dyDescent="0.25">
@@ -722,7 +755,7 @@
         <v>4</v>
       </c>
       <c r="B38">
-        <v>64</v>
+        <v>42</v>
       </c>
     </row>
     <row r="39" spans="1:2" x14ac:dyDescent="0.25">
@@ -730,7 +763,7 @@
         <v>4</v>
       </c>
       <c r="B39">
-        <v>65</v>
+        <v>45</v>
       </c>
     </row>
     <row r="40" spans="1:2" x14ac:dyDescent="0.25">
@@ -738,7 +771,7 @@
         <v>4</v>
       </c>
       <c r="B40">
-        <v>68</v>
+        <v>49</v>
       </c>
     </row>
     <row r="41" spans="1:2" x14ac:dyDescent="0.25">
@@ -746,7 +779,7 @@
         <v>4</v>
       </c>
       <c r="B41">
-        <v>70</v>
+        <v>51</v>
       </c>
     </row>
     <row r="42" spans="1:2" x14ac:dyDescent="0.25">
@@ -754,7 +787,7 @@
         <v>4</v>
       </c>
       <c r="B42">
-        <v>72</v>
+        <v>52</v>
       </c>
     </row>
     <row r="43" spans="1:2" x14ac:dyDescent="0.25">
@@ -762,7 +795,7 @@
         <v>4</v>
       </c>
       <c r="B43">
-        <v>74</v>
+        <v>56</v>
       </c>
     </row>
     <row r="44" spans="1:2" x14ac:dyDescent="0.25">
@@ -770,7 +803,7 @@
         <v>4</v>
       </c>
       <c r="B44">
-        <v>76</v>
+        <v>57</v>
       </c>
     </row>
     <row r="45" spans="1:2" x14ac:dyDescent="0.25">
@@ -778,7 +811,7 @@
         <v>4</v>
       </c>
       <c r="B45">
-        <v>77</v>
+        <v>61</v>
       </c>
     </row>
     <row r="46" spans="1:2" x14ac:dyDescent="0.25">
@@ -786,7 +819,7 @@
         <v>4</v>
       </c>
       <c r="B46">
-        <v>78</v>
+        <v>62</v>
       </c>
     </row>
     <row r="47" spans="1:2" x14ac:dyDescent="0.25">
@@ -794,7 +827,7 @@
         <v>4</v>
       </c>
       <c r="B47">
-        <v>81</v>
+        <v>63</v>
       </c>
     </row>
     <row r="48" spans="1:2" x14ac:dyDescent="0.25">
@@ -802,7 +835,7 @@
         <v>4</v>
       </c>
       <c r="B48">
-        <v>86</v>
+        <v>64</v>
       </c>
     </row>
     <row r="49" spans="1:2" x14ac:dyDescent="0.25">
@@ -810,7 +843,7 @@
         <v>4</v>
       </c>
       <c r="B49">
-        <v>87</v>
+        <v>65</v>
       </c>
     </row>
     <row r="50" spans="1:2" x14ac:dyDescent="0.25">
@@ -818,7 +851,7 @@
         <v>4</v>
       </c>
       <c r="B50">
-        <v>92</v>
+        <v>68</v>
       </c>
     </row>
     <row r="51" spans="1:2" x14ac:dyDescent="0.25">
@@ -826,7 +859,7 @@
         <v>4</v>
       </c>
       <c r="B51">
-        <v>94</v>
+        <v>70</v>
       </c>
     </row>
     <row r="52" spans="1:2" x14ac:dyDescent="0.25">
@@ -834,7 +867,7 @@
         <v>4</v>
       </c>
       <c r="B52">
-        <v>95</v>
+        <v>72</v>
       </c>
     </row>
     <row r="53" spans="1:2" x14ac:dyDescent="0.25">
@@ -842,7 +875,7 @@
         <v>4</v>
       </c>
       <c r="B53">
-        <v>97</v>
+        <v>74</v>
       </c>
     </row>
     <row r="54" spans="1:2" x14ac:dyDescent="0.25">
@@ -850,7 +883,7 @@
         <v>4</v>
       </c>
       <c r="B54">
-        <v>98</v>
+        <v>76</v>
       </c>
     </row>
     <row r="55" spans="1:2" x14ac:dyDescent="0.25">
@@ -858,7 +891,7 @@
         <v>4</v>
       </c>
       <c r="B55">
-        <v>99</v>
+        <v>77</v>
       </c>
     </row>
     <row r="56" spans="1:2" x14ac:dyDescent="0.25">
@@ -866,7 +899,7 @@
         <v>4</v>
       </c>
       <c r="B56">
-        <v>100</v>
+        <v>78</v>
       </c>
     </row>
     <row r="57" spans="1:2" x14ac:dyDescent="0.25">
@@ -874,7 +907,7 @@
         <v>4</v>
       </c>
       <c r="B57">
-        <v>103</v>
+        <v>81</v>
       </c>
     </row>
     <row r="58" spans="1:2" x14ac:dyDescent="0.25">
@@ -882,7 +915,7 @@
         <v>4</v>
       </c>
       <c r="B58">
-        <v>104</v>
+        <v>86</v>
       </c>
     </row>
     <row r="59" spans="1:2" x14ac:dyDescent="0.25">
@@ -890,7 +923,7 @@
         <v>4</v>
       </c>
       <c r="B59">
-        <v>105</v>
+        <v>87</v>
       </c>
     </row>
     <row r="60" spans="1:2" x14ac:dyDescent="0.25">
@@ -898,7 +931,7 @@
         <v>4</v>
       </c>
       <c r="B60">
-        <v>106</v>
+        <v>92</v>
       </c>
     </row>
     <row r="61" spans="1:2" x14ac:dyDescent="0.25">
@@ -906,7 +939,7 @@
         <v>4</v>
       </c>
       <c r="B61">
-        <v>107</v>
+        <v>94</v>
       </c>
     </row>
     <row r="62" spans="1:2" x14ac:dyDescent="0.25">
@@ -914,7 +947,7 @@
         <v>4</v>
       </c>
       <c r="B62">
-        <v>109</v>
+        <v>95</v>
       </c>
     </row>
     <row r="63" spans="1:2" x14ac:dyDescent="0.25">
@@ -922,7 +955,7 @@
         <v>4</v>
       </c>
       <c r="B63">
-        <v>110</v>
+        <v>97</v>
       </c>
     </row>
     <row r="64" spans="1:2" x14ac:dyDescent="0.25">
@@ -930,7 +963,7 @@
         <v>4</v>
       </c>
       <c r="B64">
-        <v>112</v>
+        <v>98</v>
       </c>
     </row>
     <row r="65" spans="1:2" x14ac:dyDescent="0.25">
@@ -938,7 +971,7 @@
         <v>4</v>
       </c>
       <c r="B65">
-        <v>114</v>
+        <v>99</v>
       </c>
     </row>
     <row r="66" spans="1:2" x14ac:dyDescent="0.25">
@@ -946,7 +979,7 @@
         <v>4</v>
       </c>
       <c r="B66">
-        <v>115</v>
+        <v>100</v>
       </c>
     </row>
     <row r="67" spans="1:2" x14ac:dyDescent="0.25">
@@ -954,7 +987,7 @@
         <v>4</v>
       </c>
       <c r="B67">
-        <v>117</v>
+        <v>103</v>
       </c>
     </row>
     <row r="68" spans="1:2" x14ac:dyDescent="0.25">
@@ -962,7 +995,7 @@
         <v>4</v>
       </c>
       <c r="B68">
-        <v>124</v>
+        <v>104</v>
       </c>
     </row>
     <row r="69" spans="1:2" x14ac:dyDescent="0.25">
@@ -970,7 +1003,7 @@
         <v>4</v>
       </c>
       <c r="B69">
-        <v>125</v>
+        <v>105</v>
       </c>
     </row>
     <row r="70" spans="1:2" x14ac:dyDescent="0.25">
@@ -978,7 +1011,7 @@
         <v>4</v>
       </c>
       <c r="B70">
-        <v>126</v>
+        <v>106</v>
       </c>
     </row>
     <row r="71" spans="1:2" x14ac:dyDescent="0.25">
@@ -986,7 +1019,7 @@
         <v>4</v>
       </c>
       <c r="B71">
-        <v>128</v>
+        <v>107</v>
       </c>
     </row>
     <row r="72" spans="1:2" x14ac:dyDescent="0.25">
@@ -994,7 +1027,7 @@
         <v>4</v>
       </c>
       <c r="B72">
-        <v>130</v>
+        <v>109</v>
       </c>
     </row>
     <row r="73" spans="1:2" x14ac:dyDescent="0.25">
@@ -1002,7 +1035,7 @@
         <v>4</v>
       </c>
       <c r="B73">
-        <v>131</v>
+        <v>110</v>
       </c>
     </row>
     <row r="74" spans="1:2" x14ac:dyDescent="0.25">
@@ -1010,7 +1043,7 @@
         <v>4</v>
       </c>
       <c r="B74">
-        <v>134</v>
+        <v>112</v>
       </c>
     </row>
     <row r="75" spans="1:2" x14ac:dyDescent="0.25">
@@ -1018,7 +1051,7 @@
         <v>4</v>
       </c>
       <c r="B75">
-        <v>137</v>
+        <v>114</v>
       </c>
     </row>
     <row r="76" spans="1:2" x14ac:dyDescent="0.25">
@@ -1026,7 +1059,7 @@
         <v>4</v>
       </c>
       <c r="B76">
-        <v>138</v>
+        <v>115</v>
       </c>
     </row>
     <row r="77" spans="1:2" x14ac:dyDescent="0.25">
@@ -1034,7 +1067,7 @@
         <v>4</v>
       </c>
       <c r="B77">
-        <v>142</v>
+        <v>117</v>
       </c>
     </row>
     <row r="78" spans="1:2" x14ac:dyDescent="0.25">
@@ -1042,7 +1075,7 @@
         <v>4</v>
       </c>
       <c r="B78">
-        <v>146</v>
+        <v>124</v>
       </c>
     </row>
     <row r="79" spans="1:2" x14ac:dyDescent="0.25">
@@ -1050,7 +1083,7 @@
         <v>4</v>
       </c>
       <c r="B79">
-        <v>148</v>
+        <v>125</v>
       </c>
     </row>
     <row r="80" spans="1:2" x14ac:dyDescent="0.25">
@@ -1058,7 +1091,7 @@
         <v>4</v>
       </c>
       <c r="B80">
-        <v>149</v>
+        <v>126</v>
       </c>
     </row>
     <row r="81" spans="1:2" x14ac:dyDescent="0.25">
@@ -1066,7 +1099,7 @@
         <v>4</v>
       </c>
       <c r="B81">
-        <v>150</v>
+        <v>128</v>
       </c>
     </row>
     <row r="82" spans="1:2" x14ac:dyDescent="0.25">
@@ -1074,7 +1107,7 @@
         <v>4</v>
       </c>
       <c r="B82">
-        <v>151</v>
+        <v>130</v>
       </c>
     </row>
     <row r="83" spans="1:2" x14ac:dyDescent="0.25">
@@ -1082,7 +1115,7 @@
         <v>4</v>
       </c>
       <c r="B83">
-        <v>154</v>
+        <v>131</v>
       </c>
     </row>
     <row r="84" spans="1:2" x14ac:dyDescent="0.25">
@@ -1090,7 +1123,7 @@
         <v>4</v>
       </c>
       <c r="B84">
-        <v>155</v>
+        <v>134</v>
       </c>
     </row>
     <row r="85" spans="1:2" x14ac:dyDescent="0.25">
@@ -1098,7 +1131,7 @@
         <v>4</v>
       </c>
       <c r="B85">
-        <v>158</v>
+        <v>137</v>
       </c>
     </row>
     <row r="86" spans="1:2" x14ac:dyDescent="0.25">
@@ -1106,7 +1139,7 @@
         <v>4</v>
       </c>
       <c r="B86">
-        <v>159</v>
+        <v>138</v>
       </c>
     </row>
     <row r="87" spans="1:2" x14ac:dyDescent="0.25">
@@ -1114,7 +1147,7 @@
         <v>4</v>
       </c>
       <c r="B87">
-        <v>161</v>
+        <v>142</v>
       </c>
     </row>
     <row r="88" spans="1:2" x14ac:dyDescent="0.25">
@@ -1122,7 +1155,7 @@
         <v>4</v>
       </c>
       <c r="B88">
-        <v>167</v>
+        <v>146</v>
       </c>
     </row>
     <row r="89" spans="1:2" x14ac:dyDescent="0.25">
@@ -1130,7 +1163,7 @@
         <v>4</v>
       </c>
       <c r="B89">
-        <v>172</v>
+        <v>148</v>
       </c>
     </row>
     <row r="90" spans="1:2" x14ac:dyDescent="0.25">
@@ -1138,7 +1171,7 @@
         <v>4</v>
       </c>
       <c r="B90">
-        <v>175</v>
+        <v>149</v>
       </c>
     </row>
     <row r="91" spans="1:2" x14ac:dyDescent="0.25">
@@ -1146,7 +1179,7 @@
         <v>4</v>
       </c>
       <c r="B91">
-        <v>176</v>
+        <v>150</v>
       </c>
     </row>
     <row r="92" spans="1:2" x14ac:dyDescent="0.25">
@@ -1154,7 +1187,7 @@
         <v>4</v>
       </c>
       <c r="B92">
-        <v>177</v>
+        <v>151</v>
       </c>
     </row>
     <row r="93" spans="1:2" x14ac:dyDescent="0.25">
@@ -1162,7 +1195,7 @@
         <v>4</v>
       </c>
       <c r="B93">
-        <v>178</v>
+        <v>154</v>
       </c>
     </row>
     <row r="94" spans="1:2" x14ac:dyDescent="0.25">
@@ -1170,7 +1203,7 @@
         <v>4</v>
       </c>
       <c r="B94">
-        <v>179</v>
+        <v>155</v>
       </c>
     </row>
     <row r="95" spans="1:2" x14ac:dyDescent="0.25">
@@ -1178,7 +1211,7 @@
         <v>4</v>
       </c>
       <c r="B95">
-        <v>180</v>
+        <v>158</v>
       </c>
     </row>
     <row r="96" spans="1:2" x14ac:dyDescent="0.25">
@@ -1186,7 +1219,7 @@
         <v>4</v>
       </c>
       <c r="B96">
-        <v>181</v>
+        <v>159</v>
       </c>
     </row>
     <row r="97" spans="1:2" x14ac:dyDescent="0.25">
@@ -1194,7 +1227,7 @@
         <v>4</v>
       </c>
       <c r="B97">
-        <v>182</v>
+        <v>161</v>
       </c>
     </row>
     <row r="98" spans="1:2" x14ac:dyDescent="0.25">
@@ -1202,7 +1235,7 @@
         <v>4</v>
       </c>
       <c r="B98">
-        <v>183</v>
+        <v>167</v>
       </c>
     </row>
     <row r="99" spans="1:2" x14ac:dyDescent="0.25">
@@ -1210,7 +1243,7 @@
         <v>4</v>
       </c>
       <c r="B99">
-        <v>186</v>
+        <v>172</v>
       </c>
     </row>
     <row r="100" spans="1:2" x14ac:dyDescent="0.25">
@@ -1218,7 +1251,7 @@
         <v>4</v>
       </c>
       <c r="B100">
-        <v>187</v>
+        <v>175</v>
       </c>
     </row>
     <row r="101" spans="1:2" x14ac:dyDescent="0.25">
@@ -1226,7 +1259,7 @@
         <v>4</v>
       </c>
       <c r="B101">
-        <v>188</v>
+        <v>176</v>
       </c>
     </row>
     <row r="102" spans="1:2" x14ac:dyDescent="0.25">
@@ -1234,7 +1267,7 @@
         <v>4</v>
       </c>
       <c r="B102">
-        <v>193</v>
+        <v>177</v>
       </c>
     </row>
     <row r="103" spans="1:2" x14ac:dyDescent="0.25">
@@ -1242,7 +1275,7 @@
         <v>4</v>
       </c>
       <c r="B103">
-        <v>195</v>
+        <v>178</v>
       </c>
     </row>
     <row r="104" spans="1:2" x14ac:dyDescent="0.25">
@@ -1250,7 +1283,7 @@
         <v>4</v>
       </c>
       <c r="B104">
-        <v>198</v>
+        <v>179</v>
       </c>
     </row>
     <row r="105" spans="1:2" x14ac:dyDescent="0.25">
@@ -1258,7 +1291,7 @@
         <v>4</v>
       </c>
       <c r="B105">
-        <v>199</v>
+        <v>180</v>
       </c>
     </row>
     <row r="106" spans="1:2" x14ac:dyDescent="0.25">
@@ -1266,7 +1299,7 @@
         <v>4</v>
       </c>
       <c r="B106">
-        <v>201</v>
+        <v>181</v>
       </c>
     </row>
     <row r="107" spans="1:2" x14ac:dyDescent="0.25">
@@ -1274,7 +1307,7 @@
         <v>4</v>
       </c>
       <c r="B107">
-        <v>204</v>
+        <v>182</v>
       </c>
     </row>
     <row r="108" spans="1:2" x14ac:dyDescent="0.25">
@@ -1282,7 +1315,7 @@
         <v>4</v>
       </c>
       <c r="B108">
-        <v>205</v>
+        <v>183</v>
       </c>
     </row>
     <row r="109" spans="1:2" x14ac:dyDescent="0.25">
@@ -1290,7 +1323,7 @@
         <v>4</v>
       </c>
       <c r="B109">
-        <v>206</v>
+        <v>186</v>
       </c>
     </row>
     <row r="110" spans="1:2" x14ac:dyDescent="0.25">
@@ -1298,7 +1331,7 @@
         <v>4</v>
       </c>
       <c r="B110">
-        <v>208</v>
+        <v>187</v>
       </c>
     </row>
     <row r="111" spans="1:2" x14ac:dyDescent="0.25">
@@ -1306,7 +1339,7 @@
         <v>4</v>
       </c>
       <c r="B111">
-        <v>211</v>
+        <v>188</v>
       </c>
     </row>
     <row r="112" spans="1:2" x14ac:dyDescent="0.25">
@@ -1314,7 +1347,7 @@
         <v>4</v>
       </c>
       <c r="B112">
-        <v>212</v>
+        <v>193</v>
       </c>
     </row>
     <row r="113" spans="1:2" x14ac:dyDescent="0.25">
@@ -1322,7 +1355,7 @@
         <v>4</v>
       </c>
       <c r="B113">
-        <v>214</v>
+        <v>195</v>
       </c>
     </row>
     <row r="114" spans="1:2" x14ac:dyDescent="0.25">
@@ -1330,7 +1363,7 @@
         <v>4</v>
       </c>
       <c r="B114">
-        <v>216</v>
+        <v>198</v>
       </c>
     </row>
     <row r="115" spans="1:2" x14ac:dyDescent="0.25">
@@ -1338,7 +1371,7 @@
         <v>4</v>
       </c>
       <c r="B115">
-        <v>217</v>
+        <v>199</v>
       </c>
     </row>
     <row r="116" spans="1:2" x14ac:dyDescent="0.25">
@@ -1346,7 +1379,7 @@
         <v>4</v>
       </c>
       <c r="B116">
-        <v>218</v>
+        <v>201</v>
       </c>
     </row>
     <row r="117" spans="1:2" x14ac:dyDescent="0.25">
@@ -1354,7 +1387,7 @@
         <v>4</v>
       </c>
       <c r="B117">
-        <v>220</v>
+        <v>204</v>
       </c>
     </row>
     <row r="118" spans="1:2" x14ac:dyDescent="0.25">
@@ -1362,7 +1395,7 @@
         <v>4</v>
       </c>
       <c r="B118">
-        <v>221</v>
+        <v>205</v>
       </c>
     </row>
     <row r="119" spans="1:2" x14ac:dyDescent="0.25">
@@ -1370,7 +1403,7 @@
         <v>4</v>
       </c>
       <c r="B119">
-        <v>222</v>
+        <v>206</v>
       </c>
     </row>
     <row r="120" spans="1:2" x14ac:dyDescent="0.25">
@@ -1378,7 +1411,7 @@
         <v>4</v>
       </c>
       <c r="B120">
-        <v>227</v>
+        <v>208</v>
       </c>
     </row>
     <row r="121" spans="1:2" x14ac:dyDescent="0.25">
@@ -1386,7 +1419,7 @@
         <v>4</v>
       </c>
       <c r="B121">
-        <v>231</v>
+        <v>211</v>
       </c>
     </row>
     <row r="122" spans="1:2" x14ac:dyDescent="0.25">
@@ -1394,7 +1427,7 @@
         <v>4</v>
       </c>
       <c r="B122">
-        <v>233</v>
+        <v>212</v>
       </c>
     </row>
     <row r="123" spans="1:2" x14ac:dyDescent="0.25">
@@ -1402,7 +1435,7 @@
         <v>4</v>
       </c>
       <c r="B123">
-        <v>235</v>
+        <v>214</v>
       </c>
     </row>
     <row r="124" spans="1:2" x14ac:dyDescent="0.25">
@@ -1410,7 +1443,7 @@
         <v>4</v>
       </c>
       <c r="B124">
-        <v>236</v>
+        <v>216</v>
       </c>
     </row>
     <row r="125" spans="1:2" x14ac:dyDescent="0.25">
@@ -1418,7 +1451,7 @@
         <v>4</v>
       </c>
       <c r="B125">
-        <v>237</v>
+        <v>217</v>
       </c>
     </row>
     <row r="126" spans="1:2" x14ac:dyDescent="0.25">
@@ -1426,7 +1459,7 @@
         <v>4</v>
       </c>
       <c r="B126">
-        <v>238</v>
+        <v>218</v>
       </c>
     </row>
     <row r="127" spans="1:2" x14ac:dyDescent="0.25">
@@ -1434,7 +1467,7 @@
         <v>4</v>
       </c>
       <c r="B127">
-        <v>241</v>
+        <v>220</v>
       </c>
     </row>
     <row r="128" spans="1:2" x14ac:dyDescent="0.25">
@@ -1442,7 +1475,7 @@
         <v>4</v>
       </c>
       <c r="B128">
-        <v>242</v>
+        <v>221</v>
       </c>
     </row>
     <row r="129" spans="1:2" x14ac:dyDescent="0.25">
@@ -1450,7 +1483,7 @@
         <v>4</v>
       </c>
       <c r="B129">
-        <v>246</v>
+        <v>222</v>
       </c>
     </row>
     <row r="130" spans="1:2" x14ac:dyDescent="0.25">
@@ -1458,7 +1491,7 @@
         <v>4</v>
       </c>
       <c r="B130">
-        <v>249</v>
+        <v>227</v>
       </c>
     </row>
     <row r="131" spans="1:2" x14ac:dyDescent="0.25">
@@ -1466,7 +1499,7 @@
         <v>4</v>
       </c>
       <c r="B131">
-        <v>251</v>
+        <v>229</v>
       </c>
     </row>
     <row r="132" spans="1:2" x14ac:dyDescent="0.25">
@@ -1474,7 +1507,7 @@
         <v>4</v>
       </c>
       <c r="B132">
-        <v>252</v>
+        <v>231</v>
       </c>
     </row>
     <row r="133" spans="1:2" x14ac:dyDescent="0.25">
@@ -1482,7 +1515,7 @@
         <v>4</v>
       </c>
       <c r="B133">
-        <v>253</v>
+        <v>233</v>
       </c>
     </row>
     <row r="134" spans="1:2" x14ac:dyDescent="0.25">
@@ -1490,7 +1523,7 @@
         <v>4</v>
       </c>
       <c r="B134">
-        <v>257</v>
+        <v>235</v>
       </c>
     </row>
     <row r="135" spans="1:2" x14ac:dyDescent="0.25">
@@ -1498,7 +1531,7 @@
         <v>4</v>
       </c>
       <c r="B135">
-        <v>259</v>
+        <v>236</v>
       </c>
     </row>
     <row r="136" spans="1:2" x14ac:dyDescent="0.25">
@@ -1506,7 +1539,7 @@
         <v>4</v>
       </c>
       <c r="B136">
-        <v>260</v>
+        <v>237</v>
       </c>
     </row>
     <row r="137" spans="1:2" x14ac:dyDescent="0.25">
@@ -1514,7 +1547,7 @@
         <v>4</v>
       </c>
       <c r="B137">
-        <v>262</v>
+        <v>238</v>
       </c>
     </row>
     <row r="138" spans="1:2" x14ac:dyDescent="0.25">
@@ -1522,7 +1555,7 @@
         <v>4</v>
       </c>
       <c r="B138">
-        <v>265</v>
+        <v>241</v>
       </c>
     </row>
     <row r="139" spans="1:2" x14ac:dyDescent="0.25">
@@ -1530,7 +1563,7 @@
         <v>4</v>
       </c>
       <c r="B139">
-        <v>266</v>
+        <v>242</v>
       </c>
     </row>
     <row r="140" spans="1:2" x14ac:dyDescent="0.25">
@@ -1538,7 +1571,7 @@
         <v>4</v>
       </c>
       <c r="B140">
-        <v>268</v>
+        <v>246</v>
       </c>
     </row>
     <row r="141" spans="1:2" x14ac:dyDescent="0.25">
@@ -1546,7 +1579,7 @@
         <v>4</v>
       </c>
       <c r="B141">
-        <v>273</v>
+        <v>249</v>
       </c>
     </row>
     <row r="142" spans="1:2" x14ac:dyDescent="0.25">
@@ -1554,7 +1587,7 @@
         <v>4</v>
       </c>
       <c r="B142">
-        <v>274</v>
+        <v>251</v>
       </c>
     </row>
     <row r="143" spans="1:2" x14ac:dyDescent="0.25">
@@ -1562,7 +1595,7 @@
         <v>4</v>
       </c>
       <c r="B143">
-        <v>276</v>
+        <v>252</v>
       </c>
     </row>
     <row r="144" spans="1:2" x14ac:dyDescent="0.25">
@@ -1570,7 +1603,7 @@
         <v>4</v>
       </c>
       <c r="B144">
-        <v>279</v>
+        <v>253</v>
       </c>
     </row>
     <row r="145" spans="1:2" x14ac:dyDescent="0.25">
@@ -1578,7 +1611,7 @@
         <v>4</v>
       </c>
       <c r="B145">
-        <v>280</v>
+        <v>257</v>
       </c>
     </row>
     <row r="146" spans="1:2" x14ac:dyDescent="0.25">
@@ -1586,7 +1619,7 @@
         <v>4</v>
       </c>
       <c r="B146">
-        <v>284</v>
+        <v>259</v>
       </c>
     </row>
     <row r="147" spans="1:2" x14ac:dyDescent="0.25">
@@ -1594,7 +1627,7 @@
         <v>4</v>
       </c>
       <c r="B147">
-        <v>285</v>
+        <v>260</v>
       </c>
     </row>
     <row r="148" spans="1:2" x14ac:dyDescent="0.25">
@@ -1602,7 +1635,7 @@
         <v>4</v>
       </c>
       <c r="B148">
-        <v>286</v>
+        <v>262</v>
       </c>
     </row>
     <row r="149" spans="1:2" x14ac:dyDescent="0.25">
@@ -1610,7 +1643,7 @@
         <v>4</v>
       </c>
       <c r="B149">
-        <v>287</v>
+        <v>265</v>
       </c>
     </row>
     <row r="150" spans="1:2" x14ac:dyDescent="0.25">
@@ -1618,7 +1651,7 @@
         <v>4</v>
       </c>
       <c r="B150">
-        <v>288</v>
+        <v>266</v>
       </c>
     </row>
     <row r="151" spans="1:2" x14ac:dyDescent="0.25">
@@ -1626,7 +1659,7 @@
         <v>4</v>
       </c>
       <c r="B151">
-        <v>291</v>
+        <v>268</v>
       </c>
     </row>
     <row r="152" spans="1:2" x14ac:dyDescent="0.25">
@@ -1634,7 +1667,7 @@
         <v>4</v>
       </c>
       <c r="B152">
-        <v>292</v>
+        <v>273</v>
       </c>
     </row>
     <row r="153" spans="1:2" x14ac:dyDescent="0.25">
@@ -1642,7 +1675,7 @@
         <v>4</v>
       </c>
       <c r="B153">
-        <v>294</v>
+        <v>274</v>
       </c>
     </row>
     <row r="154" spans="1:2" x14ac:dyDescent="0.25">
@@ -1650,7 +1683,7 @@
         <v>4</v>
       </c>
       <c r="B154">
-        <v>297</v>
+        <v>276</v>
       </c>
     </row>
     <row r="155" spans="1:2" x14ac:dyDescent="0.25">
@@ -1658,7 +1691,7 @@
         <v>4</v>
       </c>
       <c r="B155">
-        <v>298</v>
+        <v>279</v>
       </c>
     </row>
     <row r="156" spans="1:2" x14ac:dyDescent="0.25">
@@ -1666,7 +1699,7 @@
         <v>4</v>
       </c>
       <c r="B156">
-        <v>299</v>
+        <v>280</v>
       </c>
     </row>
     <row r="157" spans="1:2" x14ac:dyDescent="0.25">
@@ -1674,7 +1707,7 @@
         <v>4</v>
       </c>
       <c r="B157">
-        <v>300</v>
+        <v>284</v>
       </c>
     </row>
     <row r="158" spans="1:2" x14ac:dyDescent="0.25">
@@ -1682,7 +1715,7 @@
         <v>4</v>
       </c>
       <c r="B158">
-        <v>301</v>
+        <v>285</v>
       </c>
     </row>
     <row r="159" spans="1:2" x14ac:dyDescent="0.25">
@@ -1690,7 +1723,7 @@
         <v>4</v>
       </c>
       <c r="B159">
-        <v>302</v>
+        <v>286</v>
       </c>
     </row>
     <row r="160" spans="1:2" x14ac:dyDescent="0.25">
@@ -1698,7 +1731,7 @@
         <v>4</v>
       </c>
       <c r="B160">
-        <v>303</v>
+        <v>287</v>
       </c>
     </row>
     <row r="161" spans="1:2" x14ac:dyDescent="0.25">
@@ -1706,7 +1739,7 @@
         <v>4</v>
       </c>
       <c r="B161">
-        <v>307</v>
+        <v>288</v>
       </c>
     </row>
     <row r="162" spans="1:2" x14ac:dyDescent="0.25">
@@ -1714,7 +1747,7 @@
         <v>4</v>
       </c>
       <c r="B162">
-        <v>308</v>
+        <v>291</v>
       </c>
     </row>
     <row r="163" spans="1:2" x14ac:dyDescent="0.25">
@@ -1722,7 +1755,7 @@
         <v>4</v>
       </c>
       <c r="B163">
-        <v>309</v>
+        <v>292</v>
       </c>
     </row>
     <row r="164" spans="1:2" x14ac:dyDescent="0.25">
@@ -1730,7 +1763,7 @@
         <v>4</v>
       </c>
       <c r="B164">
-        <v>310</v>
+        <v>294</v>
       </c>
     </row>
     <row r="165" spans="1:2" x14ac:dyDescent="0.25">
@@ -1738,7 +1771,7 @@
         <v>4</v>
       </c>
       <c r="B165">
-        <v>315</v>
+        <v>297</v>
       </c>
     </row>
     <row r="166" spans="1:2" x14ac:dyDescent="0.25">
@@ -1746,7 +1779,7 @@
         <v>4</v>
       </c>
       <c r="B166">
-        <v>316</v>
+        <v>298</v>
       </c>
     </row>
     <row r="167" spans="1:2" x14ac:dyDescent="0.25">
@@ -1754,7 +1787,7 @@
         <v>4</v>
       </c>
       <c r="B167">
-        <v>318</v>
+        <v>299</v>
       </c>
     </row>
     <row r="168" spans="1:2" x14ac:dyDescent="0.25">
@@ -1762,7 +1795,7 @@
         <v>4</v>
       </c>
       <c r="B168">
-        <v>325</v>
+        <v>300</v>
       </c>
     </row>
     <row r="169" spans="1:2" x14ac:dyDescent="0.25">
@@ -1770,7 +1803,7 @@
         <v>4</v>
       </c>
       <c r="B169">
-        <v>326</v>
+        <v>301</v>
       </c>
     </row>
     <row r="170" spans="1:2" x14ac:dyDescent="0.25">
@@ -1778,7 +1811,7 @@
         <v>4</v>
       </c>
       <c r="B170">
-        <v>330</v>
+        <v>302</v>
       </c>
     </row>
     <row r="171" spans="1:2" x14ac:dyDescent="0.25">
@@ -1786,7 +1819,7 @@
         <v>4</v>
       </c>
       <c r="B171">
-        <v>332</v>
+        <v>303</v>
       </c>
     </row>
     <row r="172" spans="1:2" x14ac:dyDescent="0.25">
@@ -1794,7 +1827,7 @@
         <v>4</v>
       </c>
       <c r="B172">
-        <v>334</v>
+        <v>307</v>
       </c>
     </row>
     <row r="173" spans="1:2" x14ac:dyDescent="0.25">
@@ -1802,7 +1835,7 @@
         <v>4</v>
       </c>
       <c r="B173">
-        <v>337</v>
+        <v>308</v>
       </c>
     </row>
     <row r="174" spans="1:2" x14ac:dyDescent="0.25">
@@ -1810,7 +1843,7 @@
         <v>4</v>
       </c>
       <c r="B174">
-        <v>338</v>
+        <v>309</v>
       </c>
     </row>
     <row r="175" spans="1:2" x14ac:dyDescent="0.25">
@@ -1818,7 +1851,7 @@
         <v>4</v>
       </c>
       <c r="B175">
-        <v>339</v>
+        <v>310</v>
       </c>
     </row>
     <row r="176" spans="1:2" x14ac:dyDescent="0.25">
@@ -1826,7 +1859,7 @@
         <v>4</v>
       </c>
       <c r="B176">
-        <v>344</v>
+        <v>315</v>
       </c>
     </row>
     <row r="177" spans="1:2" x14ac:dyDescent="0.25">
@@ -1834,7 +1867,7 @@
         <v>4</v>
       </c>
       <c r="B177">
-        <v>345</v>
+        <v>316</v>
       </c>
     </row>
     <row r="178" spans="1:2" x14ac:dyDescent="0.25">
@@ -1842,7 +1875,7 @@
         <v>4</v>
       </c>
       <c r="B178">
-        <v>346</v>
+        <v>318</v>
       </c>
     </row>
     <row r="179" spans="1:2" x14ac:dyDescent="0.25">
@@ -1850,7 +1883,7 @@
         <v>4</v>
       </c>
       <c r="B179">
-        <v>348</v>
+        <v>325</v>
       </c>
     </row>
     <row r="180" spans="1:2" x14ac:dyDescent="0.25">
@@ -1858,7 +1891,7 @@
         <v>4</v>
       </c>
       <c r="B180">
-        <v>350</v>
+        <v>326</v>
       </c>
     </row>
     <row r="181" spans="1:2" x14ac:dyDescent="0.25">
@@ -1866,7 +1899,7 @@
         <v>4</v>
       </c>
       <c r="B181">
-        <v>351</v>
+        <v>330</v>
       </c>
     </row>
     <row r="182" spans="1:2" x14ac:dyDescent="0.25">
@@ -1874,7 +1907,7 @@
         <v>4</v>
       </c>
       <c r="B182">
-        <v>355</v>
+        <v>332</v>
       </c>
     </row>
     <row r="183" spans="1:2" x14ac:dyDescent="0.25">
@@ -1882,7 +1915,7 @@
         <v>4</v>
       </c>
       <c r="B183">
-        <v>356</v>
+        <v>334</v>
       </c>
     </row>
     <row r="184" spans="1:2" x14ac:dyDescent="0.25">
@@ -1890,7 +1923,7 @@
         <v>4</v>
       </c>
       <c r="B184">
-        <v>357</v>
+        <v>337</v>
       </c>
     </row>
     <row r="185" spans="1:2" x14ac:dyDescent="0.25">
@@ -1898,7 +1931,7 @@
         <v>4</v>
       </c>
       <c r="B185">
-        <v>358</v>
+        <v>338</v>
       </c>
     </row>
     <row r="186" spans="1:2" x14ac:dyDescent="0.25">
@@ -1906,7 +1939,7 @@
         <v>4</v>
       </c>
       <c r="B186">
-        <v>359</v>
+        <v>339</v>
       </c>
     </row>
     <row r="187" spans="1:2" x14ac:dyDescent="0.25">
@@ -1914,7 +1947,7 @@
         <v>4</v>
       </c>
       <c r="B187">
-        <v>360</v>
+        <v>344</v>
       </c>
     </row>
     <row r="188" spans="1:2" x14ac:dyDescent="0.25">
@@ -1922,7 +1955,7 @@
         <v>4</v>
       </c>
       <c r="B188">
-        <v>361</v>
+        <v>345</v>
       </c>
     </row>
     <row r="189" spans="1:2" x14ac:dyDescent="0.25">
@@ -1930,7 +1963,7 @@
         <v>4</v>
       </c>
       <c r="B189">
-        <v>362</v>
+        <v>346</v>
       </c>
     </row>
     <row r="190" spans="1:2" x14ac:dyDescent="0.25">
@@ -1938,7 +1971,7 @@
         <v>4</v>
       </c>
       <c r="B190">
-        <v>368</v>
+        <v>348</v>
       </c>
     </row>
     <row r="191" spans="1:2" x14ac:dyDescent="0.25">
@@ -1946,7 +1979,7 @@
         <v>4</v>
       </c>
       <c r="B191">
-        <v>372</v>
+        <v>350</v>
       </c>
     </row>
     <row r="192" spans="1:2" x14ac:dyDescent="0.25">
@@ -1954,7 +1987,7 @@
         <v>4</v>
       </c>
       <c r="B192">
-        <v>374</v>
+        <v>351</v>
       </c>
     </row>
     <row r="193" spans="1:2" x14ac:dyDescent="0.25">
@@ -1962,7 +1995,7 @@
         <v>4</v>
       </c>
       <c r="B193">
-        <v>375</v>
+        <v>355</v>
       </c>
     </row>
     <row r="194" spans="1:2" x14ac:dyDescent="0.25">
@@ -1970,7 +2003,7 @@
         <v>4</v>
       </c>
       <c r="B194">
-        <v>376</v>
+        <v>356</v>
       </c>
     </row>
     <row r="195" spans="1:2" x14ac:dyDescent="0.25">
@@ -1978,7 +2011,7 @@
         <v>4</v>
       </c>
       <c r="B195">
-        <v>377</v>
+        <v>357</v>
       </c>
     </row>
     <row r="196" spans="1:2" x14ac:dyDescent="0.25">
@@ -1986,7 +2019,7 @@
         <v>4</v>
       </c>
       <c r="B196">
-        <v>380</v>
+        <v>358</v>
       </c>
     </row>
     <row r="197" spans="1:2" x14ac:dyDescent="0.25">
@@ -1994,7 +2027,7 @@
         <v>4</v>
       </c>
       <c r="B197">
-        <v>381</v>
+        <v>359</v>
       </c>
     </row>
     <row r="198" spans="1:2" x14ac:dyDescent="0.25">
@@ -2002,7 +2035,7 @@
         <v>4</v>
       </c>
       <c r="B198">
-        <v>382</v>
+        <v>360</v>
       </c>
     </row>
     <row r="199" spans="1:2" x14ac:dyDescent="0.25">
@@ -2010,7 +2043,7 @@
         <v>4</v>
       </c>
       <c r="B199">
-        <v>384</v>
+        <v>361</v>
       </c>
     </row>
     <row r="200" spans="1:2" x14ac:dyDescent="0.25">
@@ -2018,7 +2051,7 @@
         <v>4</v>
       </c>
       <c r="B200">
-        <v>385</v>
+        <v>362</v>
       </c>
     </row>
     <row r="201" spans="1:2" x14ac:dyDescent="0.25">
@@ -2026,7 +2059,7 @@
         <v>4</v>
       </c>
       <c r="B201">
-        <v>386</v>
+        <v>368</v>
       </c>
     </row>
     <row r="202" spans="1:2" x14ac:dyDescent="0.25">
@@ -2034,7 +2067,7 @@
         <v>4</v>
       </c>
       <c r="B202">
-        <v>389</v>
+        <v>372</v>
       </c>
     </row>
     <row r="203" spans="1:2" x14ac:dyDescent="0.25">
@@ -2042,7 +2075,7 @@
         <v>4</v>
       </c>
       <c r="B203">
-        <v>393</v>
+        <v>374</v>
       </c>
     </row>
     <row r="204" spans="1:2" x14ac:dyDescent="0.25">
@@ -2050,7 +2083,7 @@
         <v>4</v>
       </c>
       <c r="B204">
-        <v>394</v>
+        <v>375</v>
       </c>
     </row>
     <row r="205" spans="1:2" x14ac:dyDescent="0.25">
@@ -2058,7 +2091,7 @@
         <v>4</v>
       </c>
       <c r="B205">
-        <v>395</v>
+        <v>376</v>
       </c>
     </row>
     <row r="206" spans="1:2" x14ac:dyDescent="0.25">
@@ -2066,7 +2099,7 @@
         <v>4</v>
       </c>
       <c r="B206">
-        <v>397</v>
+        <v>377</v>
       </c>
     </row>
     <row r="207" spans="1:2" x14ac:dyDescent="0.25">
@@ -2074,7 +2107,7 @@
         <v>4</v>
       </c>
       <c r="B207">
-        <v>403</v>
+        <v>380</v>
       </c>
     </row>
     <row r="208" spans="1:2" x14ac:dyDescent="0.25">
@@ -2082,7 +2115,7 @@
         <v>4</v>
       </c>
       <c r="B208">
-        <v>405</v>
+        <v>381</v>
       </c>
     </row>
     <row r="209" spans="1:2" x14ac:dyDescent="0.25">
@@ -2090,7 +2123,7 @@
         <v>4</v>
       </c>
       <c r="B209">
-        <v>406</v>
+        <v>382</v>
       </c>
     </row>
     <row r="210" spans="1:2" x14ac:dyDescent="0.25">
@@ -2098,7 +2131,7 @@
         <v>4</v>
       </c>
       <c r="B210">
-        <v>407</v>
+        <v>384</v>
       </c>
     </row>
     <row r="211" spans="1:2" x14ac:dyDescent="0.25">
@@ -2106,7 +2139,7 @@
         <v>4</v>
       </c>
       <c r="B211">
-        <v>411</v>
+        <v>385</v>
       </c>
     </row>
     <row r="212" spans="1:2" x14ac:dyDescent="0.25">
@@ -2114,7 +2147,7 @@
         <v>4</v>
       </c>
       <c r="B212">
-        <v>412</v>
+        <v>386</v>
       </c>
     </row>
     <row r="213" spans="1:2" x14ac:dyDescent="0.25">
@@ -2122,7 +2155,7 @@
         <v>4</v>
       </c>
       <c r="B213">
-        <v>414</v>
+        <v>389</v>
       </c>
     </row>
     <row r="214" spans="1:2" x14ac:dyDescent="0.25">
@@ -2130,7 +2163,7 @@
         <v>4</v>
       </c>
       <c r="B214">
-        <v>422</v>
+        <v>393</v>
       </c>
     </row>
     <row r="215" spans="1:2" x14ac:dyDescent="0.25">
@@ -2138,7 +2171,7 @@
         <v>4</v>
       </c>
       <c r="B215">
-        <v>427</v>
+        <v>394</v>
       </c>
     </row>
     <row r="216" spans="1:2" x14ac:dyDescent="0.25">
@@ -2146,7 +2179,7 @@
         <v>4</v>
       </c>
       <c r="B216">
-        <v>431</v>
+        <v>395</v>
       </c>
     </row>
     <row r="217" spans="1:2" x14ac:dyDescent="0.25">
@@ -2154,7 +2187,7 @@
         <v>4</v>
       </c>
       <c r="B217">
-        <v>433</v>
+        <v>397</v>
       </c>
     </row>
     <row r="218" spans="1:2" x14ac:dyDescent="0.25">
@@ -2162,7 +2195,7 @@
         <v>4</v>
       </c>
       <c r="B218">
-        <v>434</v>
+        <v>403</v>
       </c>
     </row>
     <row r="219" spans="1:2" x14ac:dyDescent="0.25">
@@ -2170,7 +2203,7 @@
         <v>4</v>
       </c>
       <c r="B219">
-        <v>435</v>
+        <v>405</v>
       </c>
     </row>
     <row r="220" spans="1:2" x14ac:dyDescent="0.25">
@@ -2178,7 +2211,7 @@
         <v>4</v>
       </c>
       <c r="B220">
-        <v>436</v>
+        <v>406</v>
       </c>
     </row>
     <row r="221" spans="1:2" x14ac:dyDescent="0.25">
@@ -2186,7 +2219,7 @@
         <v>4</v>
       </c>
       <c r="B221">
-        <v>437</v>
+        <v>407</v>
       </c>
     </row>
     <row r="222" spans="1:2" x14ac:dyDescent="0.25">
@@ -2194,7 +2227,7 @@
         <v>4</v>
       </c>
       <c r="B222">
-        <v>439</v>
+        <v>411</v>
       </c>
     </row>
     <row r="223" spans="1:2" x14ac:dyDescent="0.25">
@@ -2202,7 +2235,7 @@
         <v>4</v>
       </c>
       <c r="B223">
-        <v>442</v>
+        <v>412</v>
       </c>
     </row>
     <row r="224" spans="1:2" x14ac:dyDescent="0.25">
@@ -2210,7 +2243,7 @@
         <v>4</v>
       </c>
       <c r="B224">
-        <v>445</v>
+        <v>414</v>
       </c>
     </row>
     <row r="225" spans="1:2" x14ac:dyDescent="0.25">
@@ -2218,7 +2251,7 @@
         <v>4</v>
       </c>
       <c r="B225">
-        <v>446</v>
+        <v>422</v>
       </c>
     </row>
     <row r="226" spans="1:2" x14ac:dyDescent="0.25">
@@ -2226,7 +2259,7 @@
         <v>4</v>
       </c>
       <c r="B226">
-        <v>447</v>
+        <v>427</v>
       </c>
     </row>
     <row r="227" spans="1:2" x14ac:dyDescent="0.25">
@@ -2234,7 +2267,7 @@
         <v>4</v>
       </c>
       <c r="B227">
-        <v>449</v>
+        <v>431</v>
       </c>
     </row>
     <row r="228" spans="1:2" x14ac:dyDescent="0.25">
@@ -2242,7 +2275,7 @@
         <v>4</v>
       </c>
       <c r="B228">
-        <v>450</v>
+        <v>433</v>
       </c>
     </row>
     <row r="229" spans="1:2" x14ac:dyDescent="0.25">
@@ -2250,7 +2283,7 @@
         <v>4</v>
       </c>
       <c r="B229">
-        <v>453</v>
+        <v>434</v>
       </c>
     </row>
     <row r="230" spans="1:2" x14ac:dyDescent="0.25">
@@ -2258,7 +2291,7 @@
         <v>4</v>
       </c>
       <c r="B230">
-        <v>454</v>
+        <v>435</v>
       </c>
     </row>
     <row r="231" spans="1:2" x14ac:dyDescent="0.25">
@@ -2266,7 +2299,7 @@
         <v>4</v>
       </c>
       <c r="B231">
-        <v>455</v>
+        <v>436</v>
       </c>
     </row>
     <row r="232" spans="1:2" x14ac:dyDescent="0.25">
@@ -2274,7 +2307,7 @@
         <v>4</v>
       </c>
       <c r="B232">
-        <v>456</v>
+        <v>437</v>
       </c>
     </row>
     <row r="233" spans="1:2" x14ac:dyDescent="0.25">
@@ -2282,7 +2315,7 @@
         <v>4</v>
       </c>
       <c r="B233">
-        <v>458</v>
+        <v>439</v>
       </c>
     </row>
     <row r="234" spans="1:2" x14ac:dyDescent="0.25">
@@ -2290,7 +2323,7 @@
         <v>4</v>
       </c>
       <c r="B234">
-        <v>459</v>
+        <v>442</v>
       </c>
     </row>
     <row r="235" spans="1:2" x14ac:dyDescent="0.25">
@@ -2298,7 +2331,7 @@
         <v>4</v>
       </c>
       <c r="B235">
-        <v>460</v>
+        <v>445</v>
       </c>
     </row>
     <row r="236" spans="1:2" x14ac:dyDescent="0.25">
@@ -2306,7 +2339,7 @@
         <v>4</v>
       </c>
       <c r="B236">
-        <v>462</v>
+        <v>446</v>
       </c>
     </row>
     <row r="237" spans="1:2" x14ac:dyDescent="0.25">
@@ -2314,7 +2347,7 @@
         <v>4</v>
       </c>
       <c r="B237">
-        <v>464</v>
+        <v>447</v>
       </c>
     </row>
     <row r="238" spans="1:2" x14ac:dyDescent="0.25">
@@ -2322,7 +2355,7 @@
         <v>4</v>
       </c>
       <c r="B238">
-        <v>465</v>
+        <v>449</v>
       </c>
     </row>
     <row r="239" spans="1:2" x14ac:dyDescent="0.25">
@@ -2330,7 +2363,7 @@
         <v>4</v>
       </c>
       <c r="B239">
-        <v>466</v>
+        <v>450</v>
       </c>
     </row>
     <row r="240" spans="1:2" x14ac:dyDescent="0.25">
@@ -2338,7 +2371,7 @@
         <v>4</v>
       </c>
       <c r="B240">
-        <v>467</v>
+        <v>453</v>
       </c>
     </row>
     <row r="241" spans="1:2" x14ac:dyDescent="0.25">
@@ -2346,7 +2379,7 @@
         <v>4</v>
       </c>
       <c r="B241">
-        <v>468</v>
+        <v>454</v>
       </c>
     </row>
     <row r="242" spans="1:2" x14ac:dyDescent="0.25">
@@ -2354,7 +2387,7 @@
         <v>4</v>
       </c>
       <c r="B242">
-        <v>469</v>
+        <v>455</v>
       </c>
     </row>
     <row r="243" spans="1:2" x14ac:dyDescent="0.25">
@@ -2362,7 +2395,7 @@
         <v>4</v>
       </c>
       <c r="B243">
-        <v>470</v>
+        <v>456</v>
       </c>
     </row>
     <row r="244" spans="1:2" x14ac:dyDescent="0.25">
@@ -2370,7 +2403,7 @@
         <v>4</v>
       </c>
       <c r="B244">
-        <v>471</v>
+        <v>458</v>
       </c>
     </row>
     <row r="245" spans="1:2" x14ac:dyDescent="0.25">
@@ -2378,7 +2411,7 @@
         <v>4</v>
       </c>
       <c r="B245">
-        <v>472</v>
+        <v>459</v>
       </c>
     </row>
     <row r="246" spans="1:2" x14ac:dyDescent="0.25">
@@ -2386,7 +2419,7 @@
         <v>4</v>
       </c>
       <c r="B246">
-        <v>473</v>
+        <v>460</v>
       </c>
     </row>
     <row r="247" spans="1:2" x14ac:dyDescent="0.25">
@@ -2394,7 +2427,7 @@
         <v>4</v>
       </c>
       <c r="B247">
-        <v>474</v>
+        <v>462</v>
       </c>
     </row>
     <row r="248" spans="1:2" x14ac:dyDescent="0.25">
@@ -2402,7 +2435,7 @@
         <v>4</v>
       </c>
       <c r="B248">
-        <v>476</v>
+        <v>464</v>
       </c>
     </row>
     <row r="249" spans="1:2" x14ac:dyDescent="0.25">
@@ -2410,7 +2443,7 @@
         <v>4</v>
       </c>
       <c r="B249">
-        <v>477</v>
+        <v>465</v>
       </c>
     </row>
     <row r="250" spans="1:2" x14ac:dyDescent="0.25">
@@ -2418,7 +2451,7 @@
         <v>4</v>
       </c>
       <c r="B250">
-        <v>478</v>
+        <v>466</v>
       </c>
     </row>
     <row r="251" spans="1:2" x14ac:dyDescent="0.25">
@@ -2426,7 +2459,7 @@
         <v>4</v>
       </c>
       <c r="B251">
-        <v>484</v>
+        <v>467</v>
       </c>
     </row>
     <row r="252" spans="1:2" x14ac:dyDescent="0.25">
@@ -2434,7 +2467,7 @@
         <v>4</v>
       </c>
       <c r="B252">
-        <v>486</v>
+        <v>468</v>
       </c>
     </row>
     <row r="253" spans="1:2" x14ac:dyDescent="0.25">
@@ -2442,7 +2475,7 @@
         <v>4</v>
       </c>
       <c r="B253">
-        <v>488</v>
+        <v>469</v>
       </c>
     </row>
     <row r="254" spans="1:2" x14ac:dyDescent="0.25">
@@ -2450,7 +2483,7 @@
         <v>4</v>
       </c>
       <c r="B254">
-        <v>490</v>
+        <v>470</v>
       </c>
     </row>
     <row r="255" spans="1:2" x14ac:dyDescent="0.25">
@@ -2458,7 +2491,7 @@
         <v>4</v>
       </c>
       <c r="B255">
-        <v>491</v>
+        <v>471</v>
       </c>
     </row>
     <row r="256" spans="1:2" x14ac:dyDescent="0.25">
@@ -2466,7 +2499,7 @@
         <v>4</v>
       </c>
       <c r="B256">
-        <v>492</v>
+        <v>472</v>
       </c>
     </row>
     <row r="257" spans="1:2" x14ac:dyDescent="0.25">
@@ -2474,7 +2507,7 @@
         <v>4</v>
       </c>
       <c r="B257">
-        <v>494</v>
+        <v>473</v>
       </c>
     </row>
     <row r="258" spans="1:2" x14ac:dyDescent="0.25">
@@ -2482,7 +2515,7 @@
         <v>4</v>
       </c>
       <c r="B258">
-        <v>495</v>
+        <v>474</v>
       </c>
     </row>
     <row r="259" spans="1:2" x14ac:dyDescent="0.25">
@@ -2490,7 +2523,7 @@
         <v>4</v>
       </c>
       <c r="B259">
-        <v>496</v>
+        <v>476</v>
       </c>
     </row>
     <row r="260" spans="1:2" x14ac:dyDescent="0.25">
@@ -2498,7 +2531,7 @@
         <v>4</v>
       </c>
       <c r="B260">
-        <v>497</v>
+        <v>477</v>
       </c>
     </row>
     <row r="261" spans="1:2" x14ac:dyDescent="0.25">
@@ -2506,7 +2539,7 @@
         <v>4</v>
       </c>
       <c r="B261">
-        <v>498</v>
+        <v>478</v>
       </c>
     </row>
     <row r="262" spans="1:2" x14ac:dyDescent="0.25">
@@ -2514,7 +2547,7 @@
         <v>4</v>
       </c>
       <c r="B262">
-        <v>499</v>
+        <v>484</v>
       </c>
     </row>
     <row r="263" spans="1:2" x14ac:dyDescent="0.25">
@@ -2522,7 +2555,7 @@
         <v>4</v>
       </c>
       <c r="B263">
-        <v>500</v>
+        <v>486</v>
       </c>
     </row>
     <row r="264" spans="1:2" x14ac:dyDescent="0.25">
@@ -2530,7 +2563,7 @@
         <v>4</v>
       </c>
       <c r="B264">
-        <v>501</v>
+        <v>488</v>
       </c>
     </row>
     <row r="265" spans="1:2" x14ac:dyDescent="0.25">
@@ -2538,7 +2571,7 @@
         <v>4</v>
       </c>
       <c r="B265">
-        <v>503</v>
+        <v>490</v>
       </c>
     </row>
     <row r="266" spans="1:2" x14ac:dyDescent="0.25">
@@ -2546,7 +2579,7 @@
         <v>4</v>
       </c>
       <c r="B266">
-        <v>506</v>
+        <v>491</v>
       </c>
     </row>
     <row r="267" spans="1:2" x14ac:dyDescent="0.25">
@@ -2554,7 +2587,7 @@
         <v>4</v>
       </c>
       <c r="B267">
-        <v>507</v>
+        <v>492</v>
       </c>
     </row>
     <row r="268" spans="1:2" x14ac:dyDescent="0.25">
@@ -2562,7 +2595,7 @@
         <v>4</v>
       </c>
       <c r="B268">
-        <v>509</v>
+        <v>494</v>
       </c>
     </row>
     <row r="269" spans="1:2" x14ac:dyDescent="0.25">
@@ -2570,7 +2603,7 @@
         <v>4</v>
       </c>
       <c r="B269">
-        <v>513</v>
+        <v>495</v>
       </c>
     </row>
     <row r="270" spans="1:2" x14ac:dyDescent="0.25">
@@ -2578,7 +2611,7 @@
         <v>4</v>
       </c>
       <c r="B270">
-        <v>514</v>
+        <v>496</v>
       </c>
     </row>
     <row r="271" spans="1:2" x14ac:dyDescent="0.25">
@@ -2586,7 +2619,7 @@
         <v>4</v>
       </c>
       <c r="B271">
-        <v>516</v>
+        <v>497</v>
       </c>
     </row>
     <row r="272" spans="1:2" x14ac:dyDescent="0.25">
@@ -2594,7 +2627,7 @@
         <v>4</v>
       </c>
       <c r="B272">
-        <v>518</v>
+        <v>498</v>
       </c>
     </row>
     <row r="273" spans="1:2" x14ac:dyDescent="0.25">
@@ -2602,7 +2635,7 @@
         <v>4</v>
       </c>
       <c r="B273">
-        <v>519</v>
+        <v>499</v>
       </c>
     </row>
     <row r="274" spans="1:2" x14ac:dyDescent="0.25">
@@ -2610,7 +2643,7 @@
         <v>4</v>
       </c>
       <c r="B274">
-        <v>522</v>
+        <v>500</v>
       </c>
     </row>
     <row r="275" spans="1:2" x14ac:dyDescent="0.25">
@@ -2618,7 +2651,7 @@
         <v>4</v>
       </c>
       <c r="B275">
-        <v>525</v>
+        <v>501</v>
       </c>
     </row>
     <row r="276" spans="1:2" x14ac:dyDescent="0.25">
@@ -2626,7 +2659,7 @@
         <v>4</v>
       </c>
       <c r="B276">
-        <v>527</v>
+        <v>503</v>
       </c>
     </row>
     <row r="277" spans="1:2" x14ac:dyDescent="0.25">
@@ -2634,7 +2667,7 @@
         <v>4</v>
       </c>
       <c r="B277">
-        <v>529</v>
+        <v>506</v>
       </c>
     </row>
     <row r="278" spans="1:2" x14ac:dyDescent="0.25">
@@ -2642,7 +2675,7 @@
         <v>4</v>
       </c>
       <c r="B278">
-        <v>531</v>
+        <v>507</v>
       </c>
     </row>
     <row r="279" spans="1:2" x14ac:dyDescent="0.25">
@@ -2650,7 +2683,7 @@
         <v>4</v>
       </c>
       <c r="B279">
-        <v>532</v>
+        <v>509</v>
       </c>
     </row>
     <row r="280" spans="1:2" x14ac:dyDescent="0.25">
@@ -2658,7 +2691,7 @@
         <v>4</v>
       </c>
       <c r="B280">
-        <v>534</v>
+        <v>513</v>
       </c>
     </row>
     <row r="281" spans="1:2" x14ac:dyDescent="0.25">
@@ -2666,7 +2699,7 @@
         <v>4</v>
       </c>
       <c r="B281">
-        <v>535</v>
+        <v>514</v>
       </c>
     </row>
     <row r="282" spans="1:2" x14ac:dyDescent="0.25">
@@ -2674,7 +2707,7 @@
         <v>4</v>
       </c>
       <c r="B282">
-        <v>536</v>
+        <v>516</v>
       </c>
     </row>
     <row r="283" spans="1:2" x14ac:dyDescent="0.25">
@@ -2682,7 +2715,7 @@
         <v>4</v>
       </c>
       <c r="B283">
-        <v>537</v>
+        <v>518</v>
       </c>
     </row>
     <row r="284" spans="1:2" x14ac:dyDescent="0.25">
@@ -2690,7 +2723,7 @@
         <v>4</v>
       </c>
       <c r="B284">
-        <v>538</v>
+        <v>519</v>
       </c>
     </row>
     <row r="285" spans="1:2" x14ac:dyDescent="0.25">
@@ -2698,7 +2731,7 @@
         <v>4</v>
       </c>
       <c r="B285">
-        <v>539</v>
+        <v>522</v>
       </c>
     </row>
     <row r="286" spans="1:2" x14ac:dyDescent="0.25">
@@ -2706,7 +2739,7 @@
         <v>4</v>
       </c>
       <c r="B286">
-        <v>540</v>
+        <v>525</v>
       </c>
     </row>
     <row r="287" spans="1:2" x14ac:dyDescent="0.25">
@@ -2714,7 +2747,7 @@
         <v>4</v>
       </c>
       <c r="B287">
-        <v>541</v>
+        <v>527</v>
       </c>
     </row>
     <row r="288" spans="1:2" x14ac:dyDescent="0.25">
@@ -2722,7 +2755,7 @@
         <v>4</v>
       </c>
       <c r="B288">
-        <v>542</v>
+        <v>529</v>
       </c>
     </row>
     <row r="289" spans="1:2" x14ac:dyDescent="0.25">
@@ -2730,7 +2763,7 @@
         <v>4</v>
       </c>
       <c r="B289">
-        <v>543</v>
+        <v>531</v>
       </c>
     </row>
     <row r="290" spans="1:2" x14ac:dyDescent="0.25">
@@ -2738,95 +2771,95 @@
         <v>4</v>
       </c>
       <c r="B290">
-        <v>546</v>
+        <v>532</v>
       </c>
     </row>
     <row r="291" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A291">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B291">
-        <v>9</v>
+        <v>534</v>
       </c>
     </row>
     <row r="292" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A292">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B292">
-        <v>46</v>
+        <v>535</v>
       </c>
     </row>
     <row r="293" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A293">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B293">
-        <v>47</v>
+        <v>536</v>
       </c>
     </row>
     <row r="294" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A294">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B294">
-        <v>50</v>
+        <v>537</v>
       </c>
     </row>
     <row r="295" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A295">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B295">
-        <v>54</v>
+        <v>538</v>
       </c>
     </row>
     <row r="296" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A296">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B296">
-        <v>55</v>
+        <v>539</v>
       </c>
     </row>
     <row r="297" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A297">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B297">
-        <v>58</v>
+        <v>540</v>
       </c>
     </row>
     <row r="298" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A298">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B298">
-        <v>59</v>
+        <v>541</v>
       </c>
     </row>
     <row r="299" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A299">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B299">
-        <v>91</v>
+        <v>542</v>
       </c>
     </row>
     <row r="300" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A300">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B300">
-        <v>127</v>
+        <v>543</v>
       </c>
     </row>
     <row r="301" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A301">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B301">
-        <v>129</v>
+        <v>546</v>
       </c>
     </row>
     <row r="302" spans="1:2" x14ac:dyDescent="0.25">
@@ -2834,7 +2867,7 @@
         <v>5</v>
       </c>
       <c r="B302">
-        <v>135</v>
+        <v>9</v>
       </c>
     </row>
     <row r="303" spans="1:2" x14ac:dyDescent="0.25">
@@ -2842,7 +2875,7 @@
         <v>5</v>
       </c>
       <c r="B303">
-        <v>156</v>
+        <v>46</v>
       </c>
     </row>
     <row r="304" spans="1:2" x14ac:dyDescent="0.25">
@@ -2850,7 +2883,7 @@
         <v>5</v>
       </c>
       <c r="B304">
-        <v>163</v>
+        <v>47</v>
       </c>
     </row>
     <row r="305" spans="1:2" x14ac:dyDescent="0.25">
@@ -2858,7 +2891,7 @@
         <v>5</v>
       </c>
       <c r="B305">
-        <v>164</v>
+        <v>50</v>
       </c>
     </row>
     <row r="306" spans="1:2" x14ac:dyDescent="0.25">
@@ -2866,7 +2899,7 @@
         <v>5</v>
       </c>
       <c r="B306">
-        <v>166</v>
+        <v>54</v>
       </c>
     </row>
     <row r="307" spans="1:2" x14ac:dyDescent="0.25">
@@ -2874,7 +2907,7 @@
         <v>5</v>
       </c>
       <c r="B307">
-        <v>169</v>
+        <v>55</v>
       </c>
     </row>
     <row r="308" spans="1:2" x14ac:dyDescent="0.25">
@@ -2882,7 +2915,7 @@
         <v>5</v>
       </c>
       <c r="B308">
-        <v>213</v>
+        <v>58</v>
       </c>
     </row>
     <row r="309" spans="1:2" x14ac:dyDescent="0.25">
@@ -2890,7 +2923,7 @@
         <v>5</v>
       </c>
       <c r="B309">
-        <v>219</v>
+        <v>59</v>
       </c>
     </row>
     <row r="310" spans="1:2" x14ac:dyDescent="0.25">
@@ -2898,7 +2931,7 @@
         <v>5</v>
       </c>
       <c r="B310">
-        <v>229</v>
+        <v>91</v>
       </c>
     </row>
     <row r="311" spans="1:2" x14ac:dyDescent="0.25">
@@ -2906,7 +2939,7 @@
         <v>5</v>
       </c>
       <c r="B311">
-        <v>244</v>
+        <v>127</v>
       </c>
     </row>
     <row r="312" spans="1:2" x14ac:dyDescent="0.25">
@@ -2914,7 +2947,7 @@
         <v>5</v>
       </c>
       <c r="B312">
-        <v>254</v>
+        <v>129</v>
       </c>
     </row>
     <row r="313" spans="1:2" x14ac:dyDescent="0.25">
@@ -2922,7 +2955,7 @@
         <v>5</v>
       </c>
       <c r="B313">
-        <v>258</v>
+        <v>135</v>
       </c>
     </row>
     <row r="314" spans="1:2" x14ac:dyDescent="0.25">
@@ -2930,7 +2963,7 @@
         <v>5</v>
       </c>
       <c r="B314">
-        <v>267</v>
+        <v>156</v>
       </c>
     </row>
     <row r="315" spans="1:2" x14ac:dyDescent="0.25">
@@ -2938,7 +2971,7 @@
         <v>5</v>
       </c>
       <c r="B315">
-        <v>270</v>
+        <v>163</v>
       </c>
     </row>
     <row r="316" spans="1:2" x14ac:dyDescent="0.25">
@@ -2946,7 +2979,7 @@
         <v>5</v>
       </c>
       <c r="B316">
-        <v>281</v>
+        <v>164</v>
       </c>
     </row>
     <row r="317" spans="1:2" x14ac:dyDescent="0.25">
@@ -2954,7 +2987,7 @@
         <v>5</v>
       </c>
       <c r="B317">
-        <v>282</v>
+        <v>166</v>
       </c>
     </row>
     <row r="318" spans="1:2" x14ac:dyDescent="0.25">
@@ -2962,7 +2995,7 @@
         <v>5</v>
       </c>
       <c r="B318">
-        <v>336</v>
+        <v>169</v>
       </c>
     </row>
     <row r="319" spans="1:2" x14ac:dyDescent="0.25">
@@ -2970,7 +3003,7 @@
         <v>5</v>
       </c>
       <c r="B319">
-        <v>353</v>
+        <v>173</v>
       </c>
     </row>
     <row r="320" spans="1:2" x14ac:dyDescent="0.25">
@@ -2978,7 +3011,7 @@
         <v>5</v>
       </c>
       <c r="B320">
-        <v>371</v>
+        <v>213</v>
       </c>
     </row>
     <row r="321" spans="1:2" x14ac:dyDescent="0.25">
@@ -2986,7 +3019,7 @@
         <v>5</v>
       </c>
       <c r="B321">
-        <v>399</v>
+        <v>219</v>
       </c>
     </row>
     <row r="322" spans="1:2" x14ac:dyDescent="0.25">
@@ -2994,7 +3027,7 @@
         <v>5</v>
       </c>
       <c r="B322">
-        <v>408</v>
+        <v>229</v>
       </c>
     </row>
     <row r="323" spans="1:2" x14ac:dyDescent="0.25">
@@ -3002,7 +3035,7 @@
         <v>5</v>
       </c>
       <c r="B323">
-        <v>428</v>
+        <v>244</v>
       </c>
     </row>
     <row r="324" spans="1:2" x14ac:dyDescent="0.25">
@@ -3010,7 +3043,7 @@
         <v>5</v>
       </c>
       <c r="B324">
-        <v>429</v>
+        <v>254</v>
       </c>
     </row>
     <row r="325" spans="1:2" x14ac:dyDescent="0.25">
@@ -3018,7 +3051,7 @@
         <v>5</v>
       </c>
       <c r="B325">
-        <v>440</v>
+        <v>258</v>
       </c>
     </row>
     <row r="326" spans="1:2" x14ac:dyDescent="0.25">
@@ -3026,7 +3059,7 @@
         <v>5</v>
       </c>
       <c r="B326">
-        <v>443</v>
+        <v>267</v>
       </c>
     </row>
     <row r="327" spans="1:2" x14ac:dyDescent="0.25">
@@ -3034,7 +3067,7 @@
         <v>5</v>
       </c>
       <c r="B327">
-        <v>475</v>
+        <v>270</v>
       </c>
     </row>
     <row r="328" spans="1:2" x14ac:dyDescent="0.25">
@@ -3042,7 +3075,7 @@
         <v>5</v>
       </c>
       <c r="B328">
-        <v>483</v>
+        <v>272</v>
       </c>
     </row>
     <row r="329" spans="1:2" x14ac:dyDescent="0.25">
@@ -3050,7 +3083,7 @@
         <v>5</v>
       </c>
       <c r="B329">
-        <v>485</v>
+        <v>281</v>
       </c>
     </row>
     <row r="330" spans="1:2" x14ac:dyDescent="0.25">
@@ -3058,7 +3091,7 @@
         <v>5</v>
       </c>
       <c r="B330">
-        <v>487</v>
+        <v>282</v>
       </c>
     </row>
     <row r="331" spans="1:2" x14ac:dyDescent="0.25">
@@ -3066,7 +3099,7 @@
         <v>5</v>
       </c>
       <c r="B331">
-        <v>493</v>
+        <v>336</v>
       </c>
     </row>
     <row r="332" spans="1:2" x14ac:dyDescent="0.25">
@@ -3074,7 +3107,7 @@
         <v>5</v>
       </c>
       <c r="B332">
-        <v>502</v>
+        <v>353</v>
       </c>
     </row>
     <row r="333" spans="1:2" x14ac:dyDescent="0.25">
@@ -3082,7 +3115,7 @@
         <v>5</v>
       </c>
       <c r="B333">
-        <v>508</v>
+        <v>371</v>
       </c>
     </row>
     <row r="334" spans="1:2" x14ac:dyDescent="0.25">
@@ -3090,127 +3123,127 @@
         <v>5</v>
       </c>
       <c r="B334">
-        <v>533</v>
+        <v>399</v>
       </c>
     </row>
     <row r="335" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A335">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B335">
-        <v>2</v>
+        <v>408</v>
       </c>
     </row>
     <row r="336" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A336">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B336">
-        <v>3</v>
+        <v>428</v>
       </c>
     </row>
     <row r="337" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A337">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B337">
-        <v>4</v>
+        <v>429</v>
       </c>
     </row>
     <row r="338" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A338">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B338">
-        <v>5</v>
+        <v>440</v>
       </c>
     </row>
     <row r="339" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A339">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B339">
-        <v>6</v>
+        <v>443</v>
       </c>
     </row>
     <row r="340" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A340">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B340">
-        <v>7</v>
+        <v>475</v>
       </c>
     </row>
     <row r="341" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A341">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B341">
-        <v>8</v>
+        <v>482</v>
       </c>
     </row>
     <row r="342" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A342">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B342">
-        <v>10</v>
+        <v>483</v>
       </c>
     </row>
     <row r="343" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A343">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B343">
-        <v>11</v>
+        <v>485</v>
       </c>
     </row>
     <row r="344" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A344">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B344">
-        <v>12</v>
+        <v>487</v>
       </c>
     </row>
     <row r="345" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A345">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B345">
-        <v>14</v>
+        <v>493</v>
       </c>
     </row>
     <row r="346" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A346">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B346">
-        <v>15</v>
+        <v>502</v>
       </c>
     </row>
     <row r="347" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A347">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B347">
-        <v>16</v>
+        <v>508</v>
       </c>
     </row>
     <row r="348" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A348">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B348">
-        <v>17</v>
+        <v>533</v>
       </c>
     </row>
     <row r="349" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A349">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B349">
-        <v>19</v>
+        <v>548</v>
       </c>
     </row>
     <row r="350" spans="1:2" x14ac:dyDescent="0.25">
@@ -3218,7 +3251,7 @@
         <v>6</v>
       </c>
       <c r="B350">
-        <v>20</v>
+        <v>2</v>
       </c>
     </row>
     <row r="351" spans="1:2" x14ac:dyDescent="0.25">
@@ -3226,7 +3259,7 @@
         <v>6</v>
       </c>
       <c r="B351">
-        <v>21</v>
+        <v>3</v>
       </c>
     </row>
     <row r="352" spans="1:2" x14ac:dyDescent="0.25">
@@ -3234,7 +3267,7 @@
         <v>6</v>
       </c>
       <c r="B352">
-        <v>23</v>
+        <v>4</v>
       </c>
     </row>
     <row r="353" spans="1:2" x14ac:dyDescent="0.25">
@@ -3242,7 +3275,7 @@
         <v>6</v>
       </c>
       <c r="B353">
-        <v>24</v>
+        <v>5</v>
       </c>
     </row>
     <row r="354" spans="1:2" x14ac:dyDescent="0.25">
@@ -3250,7 +3283,7 @@
         <v>6</v>
       </c>
       <c r="B354">
-        <v>25</v>
+        <v>6</v>
       </c>
     </row>
     <row r="355" spans="1:2" x14ac:dyDescent="0.25">
@@ -3258,7 +3291,7 @@
         <v>6</v>
       </c>
       <c r="B355">
-        <v>26</v>
+        <v>7</v>
       </c>
     </row>
     <row r="356" spans="1:2" x14ac:dyDescent="0.25">
@@ -3266,7 +3299,7 @@
         <v>6</v>
       </c>
       <c r="B356">
-        <v>27</v>
+        <v>8</v>
       </c>
     </row>
     <row r="357" spans="1:2" x14ac:dyDescent="0.25">
@@ -3274,7 +3307,7 @@
         <v>6</v>
       </c>
       <c r="B357">
-        <v>28</v>
+        <v>10</v>
       </c>
     </row>
     <row r="358" spans="1:2" x14ac:dyDescent="0.25">
@@ -3282,7 +3315,7 @@
         <v>6</v>
       </c>
       <c r="B358">
-        <v>29</v>
+        <v>11</v>
       </c>
     </row>
     <row r="359" spans="1:2" x14ac:dyDescent="0.25">
@@ -3290,7 +3323,7 @@
         <v>6</v>
       </c>
       <c r="B359">
-        <v>30</v>
+        <v>12</v>
       </c>
     </row>
     <row r="360" spans="1:2" x14ac:dyDescent="0.25">
@@ -3298,7 +3331,7 @@
         <v>6</v>
       </c>
       <c r="B360">
-        <v>32</v>
+        <v>14</v>
       </c>
     </row>
     <row r="361" spans="1:2" x14ac:dyDescent="0.25">
@@ -3306,7 +3339,7 @@
         <v>6</v>
       </c>
       <c r="B361">
-        <v>36</v>
+        <v>15</v>
       </c>
     </row>
     <row r="362" spans="1:2" x14ac:dyDescent="0.25">
@@ -3314,7 +3347,7 @@
         <v>6</v>
       </c>
       <c r="B362">
-        <v>41</v>
+        <v>16</v>
       </c>
     </row>
     <row r="363" spans="1:2" x14ac:dyDescent="0.25">
@@ -3322,7 +3355,7 @@
         <v>6</v>
       </c>
       <c r="B363">
-        <v>43</v>
+        <v>17</v>
       </c>
     </row>
     <row r="364" spans="1:2" x14ac:dyDescent="0.25">
@@ -3330,7 +3363,7 @@
         <v>6</v>
       </c>
       <c r="B364">
-        <v>44</v>
+        <v>19</v>
       </c>
     </row>
     <row r="365" spans="1:2" x14ac:dyDescent="0.25">
@@ -3338,7 +3371,7 @@
         <v>6</v>
       </c>
       <c r="B365">
-        <v>53</v>
+        <v>20</v>
       </c>
     </row>
     <row r="366" spans="1:2" x14ac:dyDescent="0.25">
@@ -3346,7 +3379,7 @@
         <v>6</v>
       </c>
       <c r="B366">
-        <v>66</v>
+        <v>21</v>
       </c>
     </row>
     <row r="367" spans="1:2" x14ac:dyDescent="0.25">
@@ -3354,7 +3387,7 @@
         <v>6</v>
       </c>
       <c r="B367">
-        <v>67</v>
+        <v>23</v>
       </c>
     </row>
     <row r="368" spans="1:2" x14ac:dyDescent="0.25">
@@ -3362,7 +3395,7 @@
         <v>6</v>
       </c>
       <c r="B368">
-        <v>71</v>
+        <v>24</v>
       </c>
     </row>
     <row r="369" spans="1:2" x14ac:dyDescent="0.25">
@@ -3370,7 +3403,7 @@
         <v>6</v>
       </c>
       <c r="B369">
-        <v>75</v>
+        <v>25</v>
       </c>
     </row>
     <row r="370" spans="1:2" x14ac:dyDescent="0.25">
@@ -3378,7 +3411,7 @@
         <v>6</v>
       </c>
       <c r="B370">
-        <v>80</v>
+        <v>26</v>
       </c>
     </row>
     <row r="371" spans="1:2" x14ac:dyDescent="0.25">
@@ -3386,7 +3419,7 @@
         <v>6</v>
       </c>
       <c r="B371">
-        <v>82</v>
+        <v>27</v>
       </c>
     </row>
     <row r="372" spans="1:2" x14ac:dyDescent="0.25">
@@ -3394,7 +3427,7 @@
         <v>6</v>
       </c>
       <c r="B372">
-        <v>84</v>
+        <v>28</v>
       </c>
     </row>
     <row r="373" spans="1:2" x14ac:dyDescent="0.25">
@@ -3402,7 +3435,7 @@
         <v>6</v>
       </c>
       <c r="B373">
-        <v>85</v>
+        <v>29</v>
       </c>
     </row>
     <row r="374" spans="1:2" x14ac:dyDescent="0.25">
@@ -3410,7 +3443,7 @@
         <v>6</v>
       </c>
       <c r="B374">
-        <v>88</v>
+        <v>30</v>
       </c>
     </row>
     <row r="375" spans="1:2" x14ac:dyDescent="0.25">
@@ -3418,7 +3451,7 @@
         <v>6</v>
       </c>
       <c r="B375">
-        <v>89</v>
+        <v>32</v>
       </c>
     </row>
     <row r="376" spans="1:2" x14ac:dyDescent="0.25">
@@ -3426,7 +3459,7 @@
         <v>6</v>
       </c>
       <c r="B376">
-        <v>90</v>
+        <v>36</v>
       </c>
     </row>
     <row r="377" spans="1:2" x14ac:dyDescent="0.25">
@@ -3434,7 +3467,7 @@
         <v>6</v>
       </c>
       <c r="B377">
-        <v>93</v>
+        <v>41</v>
       </c>
     </row>
     <row r="378" spans="1:2" x14ac:dyDescent="0.25">
@@ -3442,7 +3475,7 @@
         <v>6</v>
       </c>
       <c r="B378">
-        <v>96</v>
+        <v>43</v>
       </c>
     </row>
     <row r="379" spans="1:2" x14ac:dyDescent="0.25">
@@ -3450,7 +3483,7 @@
         <v>6</v>
       </c>
       <c r="B379">
-        <v>108</v>
+        <v>44</v>
       </c>
     </row>
     <row r="380" spans="1:2" x14ac:dyDescent="0.25">
@@ -3458,7 +3491,7 @@
         <v>6</v>
       </c>
       <c r="B380">
-        <v>111</v>
+        <v>46</v>
       </c>
     </row>
     <row r="381" spans="1:2" x14ac:dyDescent="0.25">
@@ -3466,7 +3499,7 @@
         <v>6</v>
       </c>
       <c r="B381">
-        <v>113</v>
+        <v>53</v>
       </c>
     </row>
     <row r="382" spans="1:2" x14ac:dyDescent="0.25">
@@ -3474,7 +3507,7 @@
         <v>6</v>
       </c>
       <c r="B382">
-        <v>118</v>
+        <v>66</v>
       </c>
     </row>
     <row r="383" spans="1:2" x14ac:dyDescent="0.25">
@@ -3482,7 +3515,7 @@
         <v>6</v>
       </c>
       <c r="B383">
-        <v>119</v>
+        <v>67</v>
       </c>
     </row>
     <row r="384" spans="1:2" x14ac:dyDescent="0.25">
@@ -3490,7 +3523,7 @@
         <v>6</v>
       </c>
       <c r="B384">
-        <v>122</v>
+        <v>71</v>
       </c>
     </row>
     <row r="385" spans="1:2" x14ac:dyDescent="0.25">
@@ -3498,7 +3531,7 @@
         <v>6</v>
       </c>
       <c r="B385">
-        <v>123</v>
+        <v>75</v>
       </c>
     </row>
     <row r="386" spans="1:2" x14ac:dyDescent="0.25">
@@ -3506,7 +3539,7 @@
         <v>6</v>
       </c>
       <c r="B386">
-        <v>133</v>
+        <v>80</v>
       </c>
     </row>
     <row r="387" spans="1:2" x14ac:dyDescent="0.25">
@@ -3514,7 +3547,7 @@
         <v>6</v>
       </c>
       <c r="B387">
-        <v>139</v>
+        <v>82</v>
       </c>
     </row>
     <row r="388" spans="1:2" x14ac:dyDescent="0.25">
@@ -3522,7 +3555,7 @@
         <v>6</v>
       </c>
       <c r="B388">
-        <v>141</v>
+        <v>84</v>
       </c>
     </row>
     <row r="389" spans="1:2" x14ac:dyDescent="0.25">
@@ -3530,7 +3563,7 @@
         <v>6</v>
       </c>
       <c r="B389">
-        <v>143</v>
+        <v>85</v>
       </c>
     </row>
     <row r="390" spans="1:2" x14ac:dyDescent="0.25">
@@ -3538,7 +3571,7 @@
         <v>6</v>
       </c>
       <c r="B390">
-        <v>144</v>
+        <v>88</v>
       </c>
     </row>
     <row r="391" spans="1:2" x14ac:dyDescent="0.25">
@@ -3546,7 +3579,7 @@
         <v>6</v>
       </c>
       <c r="B391">
-        <v>145</v>
+        <v>89</v>
       </c>
     </row>
     <row r="392" spans="1:2" x14ac:dyDescent="0.25">
@@ -3554,7 +3587,7 @@
         <v>6</v>
       </c>
       <c r="B392">
-        <v>152</v>
+        <v>90</v>
       </c>
     </row>
     <row r="393" spans="1:2" x14ac:dyDescent="0.25">
@@ -3562,7 +3595,7 @@
         <v>6</v>
       </c>
       <c r="B393">
-        <v>157</v>
+        <v>93</v>
       </c>
     </row>
     <row r="394" spans="1:2" x14ac:dyDescent="0.25">
@@ -3570,7 +3603,7 @@
         <v>6</v>
       </c>
       <c r="B394">
-        <v>160</v>
+        <v>96</v>
       </c>
     </row>
     <row r="395" spans="1:2" x14ac:dyDescent="0.25">
@@ -3578,7 +3611,7 @@
         <v>6</v>
       </c>
       <c r="B395">
-        <v>162</v>
+        <v>108</v>
       </c>
     </row>
     <row r="396" spans="1:2" x14ac:dyDescent="0.25">
@@ -3586,7 +3619,7 @@
         <v>6</v>
       </c>
       <c r="B396">
-        <v>165</v>
+        <v>111</v>
       </c>
     </row>
     <row r="397" spans="1:2" x14ac:dyDescent="0.25">
@@ -3594,7 +3627,7 @@
         <v>6</v>
       </c>
       <c r="B397">
-        <v>170</v>
+        <v>113</v>
       </c>
     </row>
     <row r="398" spans="1:2" x14ac:dyDescent="0.25">
@@ -3602,7 +3635,7 @@
         <v>6</v>
       </c>
       <c r="B398">
-        <v>171</v>
+        <v>118</v>
       </c>
     </row>
     <row r="399" spans="1:2" x14ac:dyDescent="0.25">
@@ -3610,7 +3643,7 @@
         <v>6</v>
       </c>
       <c r="B399">
-        <v>190</v>
+        <v>119</v>
       </c>
     </row>
     <row r="400" spans="1:2" x14ac:dyDescent="0.25">
@@ -3618,7 +3651,7 @@
         <v>6</v>
       </c>
       <c r="B400">
-        <v>192</v>
+        <v>122</v>
       </c>
     </row>
     <row r="401" spans="1:2" x14ac:dyDescent="0.25">
@@ -3626,7 +3659,7 @@
         <v>6</v>
       </c>
       <c r="B401">
-        <v>194</v>
+        <v>123</v>
       </c>
     </row>
     <row r="402" spans="1:2" x14ac:dyDescent="0.25">
@@ -3634,7 +3667,7 @@
         <v>6</v>
       </c>
       <c r="B402">
-        <v>196</v>
+        <v>133</v>
       </c>
     </row>
     <row r="403" spans="1:2" x14ac:dyDescent="0.25">
@@ -3642,7 +3675,7 @@
         <v>6</v>
       </c>
       <c r="B403">
-        <v>197</v>
+        <v>139</v>
       </c>
     </row>
     <row r="404" spans="1:2" x14ac:dyDescent="0.25">
@@ -3650,7 +3683,7 @@
         <v>6</v>
       </c>
       <c r="B404">
-        <v>200</v>
+        <v>141</v>
       </c>
     </row>
     <row r="405" spans="1:2" x14ac:dyDescent="0.25">
@@ -3658,7 +3691,7 @@
         <v>6</v>
       </c>
       <c r="B405">
-        <v>202</v>
+        <v>143</v>
       </c>
     </row>
     <row r="406" spans="1:2" x14ac:dyDescent="0.25">
@@ -3666,7 +3699,7 @@
         <v>6</v>
       </c>
       <c r="B406">
-        <v>209</v>
+        <v>144</v>
       </c>
     </row>
     <row r="407" spans="1:2" x14ac:dyDescent="0.25">
@@ -3674,7 +3707,7 @@
         <v>6</v>
       </c>
       <c r="B407">
-        <v>215</v>
+        <v>145</v>
       </c>
     </row>
     <row r="408" spans="1:2" x14ac:dyDescent="0.25">
@@ -3682,7 +3715,7 @@
         <v>6</v>
       </c>
       <c r="B408">
-        <v>223</v>
+        <v>152</v>
       </c>
     </row>
     <row r="409" spans="1:2" x14ac:dyDescent="0.25">
@@ -3690,7 +3723,7 @@
         <v>6</v>
       </c>
       <c r="B409">
-        <v>225</v>
+        <v>157</v>
       </c>
     </row>
     <row r="410" spans="1:2" x14ac:dyDescent="0.25">
@@ -3698,7 +3731,7 @@
         <v>6</v>
       </c>
       <c r="B410">
-        <v>226</v>
+        <v>160</v>
       </c>
     </row>
     <row r="411" spans="1:2" x14ac:dyDescent="0.25">
@@ -3706,7 +3739,7 @@
         <v>6</v>
       </c>
       <c r="B411">
-        <v>228</v>
+        <v>162</v>
       </c>
     </row>
     <row r="412" spans="1:2" x14ac:dyDescent="0.25">
@@ -3714,7 +3747,7 @@
         <v>6</v>
       </c>
       <c r="B412">
-        <v>232</v>
+        <v>165</v>
       </c>
     </row>
     <row r="413" spans="1:2" x14ac:dyDescent="0.25">
@@ -3722,7 +3755,7 @@
         <v>6</v>
       </c>
       <c r="B413">
-        <v>239</v>
+        <v>170</v>
       </c>
     </row>
     <row r="414" spans="1:2" x14ac:dyDescent="0.25">
@@ -3730,7 +3763,7 @@
         <v>6</v>
       </c>
       <c r="B414">
-        <v>240</v>
+        <v>171</v>
       </c>
     </row>
     <row r="415" spans="1:2" x14ac:dyDescent="0.25">
@@ -3738,7 +3771,7 @@
         <v>6</v>
       </c>
       <c r="B415">
-        <v>245</v>
+        <v>190</v>
       </c>
     </row>
     <row r="416" spans="1:2" x14ac:dyDescent="0.25">
@@ -3746,7 +3779,7 @@
         <v>6</v>
       </c>
       <c r="B416">
-        <v>247</v>
+        <v>192</v>
       </c>
     </row>
     <row r="417" spans="1:2" x14ac:dyDescent="0.25">
@@ -3754,7 +3787,7 @@
         <v>6</v>
       </c>
       <c r="B417">
-        <v>255</v>
+        <v>194</v>
       </c>
     </row>
     <row r="418" spans="1:2" x14ac:dyDescent="0.25">
@@ -3762,7 +3795,7 @@
         <v>6</v>
       </c>
       <c r="B418">
-        <v>256</v>
+        <v>196</v>
       </c>
     </row>
     <row r="419" spans="1:2" x14ac:dyDescent="0.25">
@@ -3770,7 +3803,7 @@
         <v>6</v>
       </c>
       <c r="B419">
-        <v>261</v>
+        <v>197</v>
       </c>
     </row>
     <row r="420" spans="1:2" x14ac:dyDescent="0.25">
@@ -3778,7 +3811,7 @@
         <v>6</v>
       </c>
       <c r="B420">
-        <v>264</v>
+        <v>200</v>
       </c>
     </row>
     <row r="421" spans="1:2" x14ac:dyDescent="0.25">
@@ -3786,7 +3819,7 @@
         <v>6</v>
       </c>
       <c r="B421">
-        <v>269</v>
+        <v>202</v>
       </c>
     </row>
     <row r="422" spans="1:2" x14ac:dyDescent="0.25">
@@ -3794,7 +3827,7 @@
         <v>6</v>
       </c>
       <c r="B422">
-        <v>271</v>
+        <v>209</v>
       </c>
     </row>
     <row r="423" spans="1:2" x14ac:dyDescent="0.25">
@@ -3802,7 +3835,7 @@
         <v>6</v>
       </c>
       <c r="B423">
-        <v>272</v>
+        <v>215</v>
       </c>
     </row>
     <row r="424" spans="1:2" x14ac:dyDescent="0.25">
@@ -3810,7 +3843,7 @@
         <v>6</v>
       </c>
       <c r="B424">
-        <v>275</v>
+        <v>223</v>
       </c>
     </row>
     <row r="425" spans="1:2" x14ac:dyDescent="0.25">
@@ -3818,7 +3851,7 @@
         <v>6</v>
       </c>
       <c r="B425">
-        <v>277</v>
+        <v>225</v>
       </c>
     </row>
     <row r="426" spans="1:2" x14ac:dyDescent="0.25">
@@ -3826,7 +3859,7 @@
         <v>6</v>
       </c>
       <c r="B426">
-        <v>278</v>
+        <v>226</v>
       </c>
     </row>
     <row r="427" spans="1:2" x14ac:dyDescent="0.25">
@@ -3834,7 +3867,7 @@
         <v>6</v>
       </c>
       <c r="B427">
-        <v>283</v>
+        <v>228</v>
       </c>
     </row>
     <row r="428" spans="1:2" x14ac:dyDescent="0.25">
@@ -3842,7 +3875,7 @@
         <v>6</v>
       </c>
       <c r="B428">
-        <v>289</v>
+        <v>232</v>
       </c>
     </row>
     <row r="429" spans="1:2" x14ac:dyDescent="0.25">
@@ -3850,7 +3883,7 @@
         <v>6</v>
       </c>
       <c r="B429">
-        <v>293</v>
+        <v>239</v>
       </c>
     </row>
     <row r="430" spans="1:2" x14ac:dyDescent="0.25">
@@ -3858,7 +3891,7 @@
         <v>6</v>
       </c>
       <c r="B430">
-        <v>295</v>
+        <v>240</v>
       </c>
     </row>
     <row r="431" spans="1:2" x14ac:dyDescent="0.25">
@@ -3866,7 +3899,7 @@
         <v>6</v>
       </c>
       <c r="B431">
-        <v>296</v>
+        <v>245</v>
       </c>
     </row>
     <row r="432" spans="1:2" x14ac:dyDescent="0.25">
@@ -3874,7 +3907,7 @@
         <v>6</v>
       </c>
       <c r="B432">
-        <v>306</v>
+        <v>247</v>
       </c>
     </row>
     <row r="433" spans="1:2" x14ac:dyDescent="0.25">
@@ -3882,7 +3915,7 @@
         <v>6</v>
       </c>
       <c r="B433">
-        <v>311</v>
+        <v>255</v>
       </c>
     </row>
     <row r="434" spans="1:2" x14ac:dyDescent="0.25">
@@ -3890,7 +3923,7 @@
         <v>6</v>
       </c>
       <c r="B434">
-        <v>312</v>
+        <v>256</v>
       </c>
     </row>
     <row r="435" spans="1:2" x14ac:dyDescent="0.25">
@@ -3898,7 +3931,7 @@
         <v>6</v>
       </c>
       <c r="B435">
-        <v>314</v>
+        <v>261</v>
       </c>
     </row>
     <row r="436" spans="1:2" x14ac:dyDescent="0.25">
@@ -3906,7 +3939,7 @@
         <v>6</v>
       </c>
       <c r="B436">
-        <v>317</v>
+        <v>264</v>
       </c>
     </row>
     <row r="437" spans="1:2" x14ac:dyDescent="0.25">
@@ -3914,7 +3947,7 @@
         <v>6</v>
       </c>
       <c r="B437">
-        <v>320</v>
+        <v>269</v>
       </c>
     </row>
     <row r="438" spans="1:2" x14ac:dyDescent="0.25">
@@ -3922,7 +3955,7 @@
         <v>6</v>
       </c>
       <c r="B438">
-        <v>322</v>
+        <v>271</v>
       </c>
     </row>
     <row r="439" spans="1:2" x14ac:dyDescent="0.25">
@@ -3930,7 +3963,7 @@
         <v>6</v>
       </c>
       <c r="B439">
-        <v>323</v>
+        <v>272</v>
       </c>
     </row>
     <row r="440" spans="1:2" x14ac:dyDescent="0.25">
@@ -3938,7 +3971,7 @@
         <v>6</v>
       </c>
       <c r="B440">
-        <v>324</v>
+        <v>275</v>
       </c>
     </row>
     <row r="441" spans="1:2" x14ac:dyDescent="0.25">
@@ -3946,7 +3979,7 @@
         <v>6</v>
       </c>
       <c r="B441">
-        <v>327</v>
+        <v>277</v>
       </c>
     </row>
     <row r="442" spans="1:2" x14ac:dyDescent="0.25">
@@ -3954,7 +3987,7 @@
         <v>6</v>
       </c>
       <c r="B442">
-        <v>328</v>
+        <v>278</v>
       </c>
     </row>
     <row r="443" spans="1:2" x14ac:dyDescent="0.25">
@@ -3962,7 +3995,7 @@
         <v>6</v>
       </c>
       <c r="B443">
-        <v>329</v>
+        <v>283</v>
       </c>
     </row>
     <row r="444" spans="1:2" x14ac:dyDescent="0.25">
@@ -3970,7 +4003,7 @@
         <v>6</v>
       </c>
       <c r="B444">
-        <v>333</v>
+        <v>289</v>
       </c>
     </row>
     <row r="445" spans="1:2" x14ac:dyDescent="0.25">
@@ -3978,7 +4011,7 @@
         <v>6</v>
       </c>
       <c r="B445">
-        <v>335</v>
+        <v>293</v>
       </c>
     </row>
     <row r="446" spans="1:2" x14ac:dyDescent="0.25">
@@ -3986,7 +4019,7 @@
         <v>6</v>
       </c>
       <c r="B446">
-        <v>340</v>
+        <v>295</v>
       </c>
     </row>
     <row r="447" spans="1:2" x14ac:dyDescent="0.25">
@@ -3994,7 +4027,7 @@
         <v>6</v>
       </c>
       <c r="B447">
-        <v>341</v>
+        <v>296</v>
       </c>
     </row>
     <row r="448" spans="1:2" x14ac:dyDescent="0.25">
@@ -4002,7 +4035,7 @@
         <v>6</v>
       </c>
       <c r="B448">
-        <v>342</v>
+        <v>306</v>
       </c>
     </row>
     <row r="449" spans="1:2" x14ac:dyDescent="0.25">
@@ -4010,7 +4043,7 @@
         <v>6</v>
       </c>
       <c r="B449">
-        <v>343</v>
+        <v>311</v>
       </c>
     </row>
     <row r="450" spans="1:2" x14ac:dyDescent="0.25">
@@ -4018,7 +4051,7 @@
         <v>6</v>
       </c>
       <c r="B450">
-        <v>354</v>
+        <v>312</v>
       </c>
     </row>
     <row r="451" spans="1:2" x14ac:dyDescent="0.25">
@@ -4026,7 +4059,7 @@
         <v>6</v>
       </c>
       <c r="B451">
-        <v>363</v>
+        <v>314</v>
       </c>
     </row>
     <row r="452" spans="1:2" x14ac:dyDescent="0.25">
@@ -4034,7 +4067,7 @@
         <v>6</v>
       </c>
       <c r="B452">
-        <v>364</v>
+        <v>317</v>
       </c>
     </row>
     <row r="453" spans="1:2" x14ac:dyDescent="0.25">
@@ -4042,7 +4075,7 @@
         <v>6</v>
       </c>
       <c r="B453">
-        <v>365</v>
+        <v>320</v>
       </c>
     </row>
     <row r="454" spans="1:2" x14ac:dyDescent="0.25">
@@ -4050,7 +4083,7 @@
         <v>6</v>
       </c>
       <c r="B454">
-        <v>366</v>
+        <v>322</v>
       </c>
     </row>
     <row r="455" spans="1:2" x14ac:dyDescent="0.25">
@@ -4058,7 +4091,7 @@
         <v>6</v>
       </c>
       <c r="B455">
-        <v>367</v>
+        <v>323</v>
       </c>
     </row>
     <row r="456" spans="1:2" x14ac:dyDescent="0.25">
@@ -4066,7 +4099,7 @@
         <v>6</v>
       </c>
       <c r="B456">
-        <v>369</v>
+        <v>324</v>
       </c>
     </row>
     <row r="457" spans="1:2" x14ac:dyDescent="0.25">
@@ -4074,7 +4107,7 @@
         <v>6</v>
       </c>
       <c r="B457">
-        <v>370</v>
+        <v>327</v>
       </c>
     </row>
     <row r="458" spans="1:2" x14ac:dyDescent="0.25">
@@ -4082,7 +4115,7 @@
         <v>6</v>
       </c>
       <c r="B458">
-        <v>373</v>
+        <v>328</v>
       </c>
     </row>
     <row r="459" spans="1:2" x14ac:dyDescent="0.25">
@@ -4090,7 +4123,7 @@
         <v>6</v>
       </c>
       <c r="B459">
-        <v>378</v>
+        <v>329</v>
       </c>
     </row>
     <row r="460" spans="1:2" x14ac:dyDescent="0.25">
@@ -4098,7 +4131,7 @@
         <v>6</v>
       </c>
       <c r="B460">
-        <v>379</v>
+        <v>333</v>
       </c>
     </row>
     <row r="461" spans="1:2" x14ac:dyDescent="0.25">
@@ -4106,7 +4139,7 @@
         <v>6</v>
       </c>
       <c r="B461">
-        <v>387</v>
+        <v>335</v>
       </c>
     </row>
     <row r="462" spans="1:2" x14ac:dyDescent="0.25">
@@ -4114,7 +4147,7 @@
         <v>6</v>
       </c>
       <c r="B462">
-        <v>388</v>
+        <v>340</v>
       </c>
     </row>
     <row r="463" spans="1:2" x14ac:dyDescent="0.25">
@@ -4122,7 +4155,7 @@
         <v>6</v>
       </c>
       <c r="B463">
-        <v>392</v>
+        <v>341</v>
       </c>
     </row>
     <row r="464" spans="1:2" x14ac:dyDescent="0.25">
@@ -4130,7 +4163,7 @@
         <v>6</v>
       </c>
       <c r="B464">
-        <v>396</v>
+        <v>342</v>
       </c>
     </row>
     <row r="465" spans="1:2" x14ac:dyDescent="0.25">
@@ -4138,7 +4171,7 @@
         <v>6</v>
       </c>
       <c r="B465">
-        <v>400</v>
+        <v>343</v>
       </c>
     </row>
     <row r="466" spans="1:2" x14ac:dyDescent="0.25">
@@ -4146,7 +4179,7 @@
         <v>6</v>
       </c>
       <c r="B466">
-        <v>401</v>
+        <v>354</v>
       </c>
     </row>
     <row r="467" spans="1:2" x14ac:dyDescent="0.25">
@@ -4154,7 +4187,7 @@
         <v>6</v>
       </c>
       <c r="B467">
-        <v>404</v>
+        <v>363</v>
       </c>
     </row>
     <row r="468" spans="1:2" x14ac:dyDescent="0.25">
@@ -4162,7 +4195,7 @@
         <v>6</v>
       </c>
       <c r="B468">
-        <v>410</v>
+        <v>364</v>
       </c>
     </row>
     <row r="469" spans="1:2" x14ac:dyDescent="0.25">
@@ -4170,7 +4203,7 @@
         <v>6</v>
       </c>
       <c r="B469">
-        <v>413</v>
+        <v>365</v>
       </c>
     </row>
     <row r="470" spans="1:2" x14ac:dyDescent="0.25">
@@ -4178,7 +4211,7 @@
         <v>6</v>
       </c>
       <c r="B470">
-        <v>415</v>
+        <v>366</v>
       </c>
     </row>
     <row r="471" spans="1:2" x14ac:dyDescent="0.25">
@@ -4186,7 +4219,7 @@
         <v>6</v>
       </c>
       <c r="B471">
-        <v>417</v>
+        <v>367</v>
       </c>
     </row>
     <row r="472" spans="1:2" x14ac:dyDescent="0.25">
@@ -4194,7 +4227,7 @@
         <v>6</v>
       </c>
       <c r="B472">
-        <v>418</v>
+        <v>369</v>
       </c>
     </row>
     <row r="473" spans="1:2" x14ac:dyDescent="0.25">
@@ -4202,7 +4235,7 @@
         <v>6</v>
       </c>
       <c r="B473">
-        <v>419</v>
+        <v>370</v>
       </c>
     </row>
     <row r="474" spans="1:2" x14ac:dyDescent="0.25">
@@ -4210,7 +4243,7 @@
         <v>6</v>
       </c>
       <c r="B474">
-        <v>420</v>
+        <v>373</v>
       </c>
     </row>
     <row r="475" spans="1:2" x14ac:dyDescent="0.25">
@@ -4218,7 +4251,7 @@
         <v>6</v>
       </c>
       <c r="B475">
-        <v>424</v>
+        <v>378</v>
       </c>
     </row>
     <row r="476" spans="1:2" x14ac:dyDescent="0.25">
@@ -4226,7 +4259,7 @@
         <v>6</v>
       </c>
       <c r="B476">
-        <v>425</v>
+        <v>379</v>
       </c>
     </row>
     <row r="477" spans="1:2" x14ac:dyDescent="0.25">
@@ -4234,7 +4267,7 @@
         <v>6</v>
       </c>
       <c r="B477">
-        <v>426</v>
+        <v>387</v>
       </c>
     </row>
     <row r="478" spans="1:2" x14ac:dyDescent="0.25">
@@ -4242,7 +4275,7 @@
         <v>6</v>
       </c>
       <c r="B478">
-        <v>432</v>
+        <v>388</v>
       </c>
     </row>
     <row r="479" spans="1:2" x14ac:dyDescent="0.25">
@@ -4250,7 +4283,7 @@
         <v>6</v>
       </c>
       <c r="B479">
-        <v>444</v>
+        <v>391</v>
       </c>
     </row>
     <row r="480" spans="1:2" x14ac:dyDescent="0.25">
@@ -4258,7 +4291,7 @@
         <v>6</v>
       </c>
       <c r="B480">
-        <v>448</v>
+        <v>392</v>
       </c>
     </row>
     <row r="481" spans="1:2" x14ac:dyDescent="0.25">
@@ -4266,7 +4299,7 @@
         <v>6</v>
       </c>
       <c r="B481">
-        <v>461</v>
+        <v>396</v>
       </c>
     </row>
     <row r="482" spans="1:2" x14ac:dyDescent="0.25">
@@ -4274,7 +4307,7 @@
         <v>6</v>
       </c>
       <c r="B482">
-        <v>463</v>
+        <v>400</v>
       </c>
     </row>
     <row r="483" spans="1:2" x14ac:dyDescent="0.25">
@@ -4282,7 +4315,7 @@
         <v>6</v>
       </c>
       <c r="B483">
-        <v>480</v>
+        <v>401</v>
       </c>
     </row>
     <row r="484" spans="1:2" x14ac:dyDescent="0.25">
@@ -4290,7 +4323,7 @@
         <v>6</v>
       </c>
       <c r="B484">
-        <v>481</v>
+        <v>404</v>
       </c>
     </row>
     <row r="485" spans="1:2" x14ac:dyDescent="0.25">
@@ -4298,7 +4331,7 @@
         <v>6</v>
       </c>
       <c r="B485">
-        <v>482</v>
+        <v>410</v>
       </c>
     </row>
     <row r="486" spans="1:2" x14ac:dyDescent="0.25">
@@ -4306,7 +4339,7 @@
         <v>6</v>
       </c>
       <c r="B486">
-        <v>489</v>
+        <v>413</v>
       </c>
     </row>
     <row r="487" spans="1:2" x14ac:dyDescent="0.25">
@@ -4314,7 +4347,7 @@
         <v>6</v>
       </c>
       <c r="B487">
-        <v>505</v>
+        <v>415</v>
       </c>
     </row>
     <row r="488" spans="1:2" x14ac:dyDescent="0.25">
@@ -4322,7 +4355,7 @@
         <v>6</v>
       </c>
       <c r="B488">
-        <v>512</v>
+        <v>417</v>
       </c>
     </row>
     <row r="489" spans="1:2" x14ac:dyDescent="0.25">
@@ -4330,7 +4363,7 @@
         <v>6</v>
       </c>
       <c r="B489">
-        <v>515</v>
+        <v>418</v>
       </c>
     </row>
     <row r="490" spans="1:2" x14ac:dyDescent="0.25">
@@ -4338,7 +4371,7 @@
         <v>6</v>
       </c>
       <c r="B490">
-        <v>517</v>
+        <v>419</v>
       </c>
     </row>
     <row r="491" spans="1:2" x14ac:dyDescent="0.25">
@@ -4346,7 +4379,7 @@
         <v>6</v>
       </c>
       <c r="B491">
-        <v>521</v>
+        <v>420</v>
       </c>
     </row>
     <row r="492" spans="1:2" x14ac:dyDescent="0.25">
@@ -4354,7 +4387,7 @@
         <v>6</v>
       </c>
       <c r="B492">
-        <v>523</v>
+        <v>421</v>
       </c>
     </row>
     <row r="493" spans="1:2" x14ac:dyDescent="0.25">
@@ -4362,7 +4395,7 @@
         <v>6</v>
       </c>
       <c r="B493">
-        <v>524</v>
+        <v>424</v>
       </c>
     </row>
     <row r="494" spans="1:2" x14ac:dyDescent="0.25">
@@ -4370,7 +4403,7 @@
         <v>6</v>
       </c>
       <c r="B494">
-        <v>526</v>
+        <v>425</v>
       </c>
     </row>
     <row r="495" spans="1:2" x14ac:dyDescent="0.25">
@@ -4378,7 +4411,7 @@
         <v>6</v>
       </c>
       <c r="B495">
-        <v>528</v>
+        <v>426</v>
       </c>
     </row>
     <row r="496" spans="1:2" x14ac:dyDescent="0.25">
@@ -4386,7 +4419,7 @@
         <v>6</v>
       </c>
       <c r="B496">
-        <v>545</v>
+        <v>432</v>
       </c>
     </row>
     <row r="497" spans="1:2" x14ac:dyDescent="0.25">
@@ -4394,223 +4427,223 @@
         <v>6</v>
       </c>
       <c r="B497">
-        <v>547</v>
+        <v>443</v>
       </c>
     </row>
     <row r="498" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A498">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="B498">
-        <v>83</v>
+        <v>444</v>
       </c>
     </row>
     <row r="499" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A499">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="B499">
-        <v>230</v>
+        <v>448</v>
       </c>
     </row>
     <row r="500" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A500">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="B500">
-        <v>248</v>
+        <v>461</v>
       </c>
     </row>
     <row r="501" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A501">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="B501">
-        <v>305</v>
+        <v>463</v>
       </c>
     </row>
     <row r="502" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A502">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="B502">
-        <v>548</v>
+        <v>480</v>
       </c>
     </row>
     <row r="503" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A503">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="B503">
-        <v>13</v>
+        <v>481</v>
       </c>
     </row>
     <row r="504" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A504">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="B504">
-        <v>18</v>
+        <v>482</v>
       </c>
     </row>
     <row r="505" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A505">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="B505">
-        <v>48</v>
+        <v>489</v>
       </c>
     </row>
     <row r="506" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A506">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="B506">
-        <v>69</v>
+        <v>505</v>
       </c>
     </row>
     <row r="507" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A507">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="B507">
-        <v>73</v>
+        <v>512</v>
       </c>
     </row>
     <row r="508" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A508">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="B508">
-        <v>79</v>
+        <v>515</v>
       </c>
     </row>
     <row r="509" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A509">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="B509">
-        <v>102</v>
+        <v>517</v>
       </c>
     </row>
     <row r="510" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A510">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="B510">
-        <v>116</v>
+        <v>521</v>
       </c>
     </row>
     <row r="511" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A511">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="B511">
-        <v>121</v>
+        <v>523</v>
       </c>
     </row>
     <row r="512" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A512">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="B512">
-        <v>132</v>
+        <v>524</v>
       </c>
     </row>
     <row r="513" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A513">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="B513">
-        <v>140</v>
+        <v>526</v>
       </c>
     </row>
     <row r="514" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A514">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="B514">
-        <v>147</v>
+        <v>528</v>
       </c>
     </row>
     <row r="515" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A515">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="B515">
-        <v>153</v>
+        <v>545</v>
       </c>
     </row>
     <row r="516" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A516">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="B516">
-        <v>173</v>
+        <v>547</v>
       </c>
     </row>
     <row r="517" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A517">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="B517">
-        <v>174</v>
+        <v>548</v>
       </c>
     </row>
     <row r="518" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A518">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="B518">
-        <v>184</v>
+        <v>248</v>
       </c>
     </row>
     <row r="519" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A519">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B519">
-        <v>185</v>
+        <v>83</v>
       </c>
     </row>
     <row r="520" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A520">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B520">
-        <v>191</v>
+        <v>230</v>
       </c>
     </row>
     <row r="521" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A521">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B521">
-        <v>203</v>
+        <v>248</v>
       </c>
     </row>
     <row r="522" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A522">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B522">
-        <v>210</v>
+        <v>305</v>
       </c>
     </row>
     <row r="523" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A523">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B523">
-        <v>224</v>
+        <v>438</v>
       </c>
     </row>
     <row r="524" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A524">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B524">
-        <v>234</v>
+        <v>548</v>
       </c>
     </row>
     <row r="525" spans="1:2" x14ac:dyDescent="0.25">
@@ -4618,7 +4651,7 @@
         <v>9</v>
       </c>
       <c r="B525">
-        <v>243</v>
+        <v>13</v>
       </c>
     </row>
     <row r="526" spans="1:2" x14ac:dyDescent="0.25">
@@ -4626,7 +4659,7 @@
         <v>9</v>
       </c>
       <c r="B526">
-        <v>250</v>
+        <v>18</v>
       </c>
     </row>
     <row r="527" spans="1:2" x14ac:dyDescent="0.25">
@@ -4634,7 +4667,7 @@
         <v>9</v>
       </c>
       <c r="B527">
-        <v>263</v>
+        <v>48</v>
       </c>
     </row>
     <row r="528" spans="1:2" x14ac:dyDescent="0.25">
@@ -4642,7 +4675,7 @@
         <v>9</v>
       </c>
       <c r="B528">
-        <v>313</v>
+        <v>69</v>
       </c>
     </row>
     <row r="529" spans="1:2" x14ac:dyDescent="0.25">
@@ -4650,7 +4683,7 @@
         <v>9</v>
       </c>
       <c r="B529">
-        <v>319</v>
+        <v>73</v>
       </c>
     </row>
     <row r="530" spans="1:2" x14ac:dyDescent="0.25">
@@ -4658,7 +4691,7 @@
         <v>9</v>
       </c>
       <c r="B530">
-        <v>331</v>
+        <v>79</v>
       </c>
     </row>
     <row r="531" spans="1:2" x14ac:dyDescent="0.25">
@@ -4666,7 +4699,7 @@
         <v>9</v>
       </c>
       <c r="B531">
-        <v>349</v>
+        <v>102</v>
       </c>
     </row>
     <row r="532" spans="1:2" x14ac:dyDescent="0.25">
@@ -4674,7 +4707,7 @@
         <v>9</v>
       </c>
       <c r="B532">
-        <v>352</v>
+        <v>116</v>
       </c>
     </row>
     <row r="533" spans="1:2" x14ac:dyDescent="0.25">
@@ -4682,7 +4715,7 @@
         <v>9</v>
       </c>
       <c r="B533">
-        <v>390</v>
+        <v>121</v>
       </c>
     </row>
     <row r="534" spans="1:2" x14ac:dyDescent="0.25">
@@ -4690,7 +4723,7 @@
         <v>9</v>
       </c>
       <c r="B534">
-        <v>398</v>
+        <v>132</v>
       </c>
     </row>
     <row r="535" spans="1:2" x14ac:dyDescent="0.25">
@@ -4698,7 +4731,7 @@
         <v>9</v>
       </c>
       <c r="B535">
-        <v>402</v>
+        <v>140</v>
       </c>
     </row>
     <row r="536" spans="1:2" x14ac:dyDescent="0.25">
@@ -4706,7 +4739,7 @@
         <v>9</v>
       </c>
       <c r="B536">
-        <v>409</v>
+        <v>145</v>
       </c>
     </row>
     <row r="537" spans="1:2" x14ac:dyDescent="0.25">
@@ -4714,7 +4747,7 @@
         <v>9</v>
       </c>
       <c r="B537">
-        <v>416</v>
+        <v>147</v>
       </c>
     </row>
     <row r="538" spans="1:2" x14ac:dyDescent="0.25">
@@ -4722,7 +4755,7 @@
         <v>9</v>
       </c>
       <c r="B538">
-        <v>430</v>
+        <v>153</v>
       </c>
     </row>
     <row r="539" spans="1:2" x14ac:dyDescent="0.25">
@@ -4730,7 +4763,7 @@
         <v>9</v>
       </c>
       <c r="B539">
-        <v>438</v>
+        <v>173</v>
       </c>
     </row>
     <row r="540" spans="1:2" x14ac:dyDescent="0.25">
@@ -4738,7 +4771,7 @@
         <v>9</v>
       </c>
       <c r="B540">
-        <v>441</v>
+        <v>174</v>
       </c>
     </row>
     <row r="541" spans="1:2" x14ac:dyDescent="0.25">
@@ -4746,7 +4779,7 @@
         <v>9</v>
       </c>
       <c r="B541">
-        <v>451</v>
+        <v>184</v>
       </c>
     </row>
     <row r="542" spans="1:2" x14ac:dyDescent="0.25">
@@ -4754,7 +4787,7 @@
         <v>9</v>
       </c>
       <c r="B542">
-        <v>452</v>
+        <v>185</v>
       </c>
     </row>
     <row r="543" spans="1:2" x14ac:dyDescent="0.25">
@@ -4762,7 +4795,7 @@
         <v>9</v>
       </c>
       <c r="B543">
-        <v>457</v>
+        <v>191</v>
       </c>
     </row>
     <row r="544" spans="1:2" x14ac:dyDescent="0.25">
@@ -4770,7 +4803,7 @@
         <v>9</v>
       </c>
       <c r="B544">
-        <v>479</v>
+        <v>203</v>
       </c>
     </row>
     <row r="545" spans="1:2" x14ac:dyDescent="0.25">
@@ -4778,7 +4811,7 @@
         <v>9</v>
       </c>
       <c r="B545">
-        <v>504</v>
+        <v>210</v>
       </c>
     </row>
     <row r="546" spans="1:2" x14ac:dyDescent="0.25">
@@ -4786,7 +4819,7 @@
         <v>9</v>
       </c>
       <c r="B546">
-        <v>510</v>
+        <v>213</v>
       </c>
     </row>
     <row r="547" spans="1:2" x14ac:dyDescent="0.25">
@@ -4794,7 +4827,7 @@
         <v>9</v>
       </c>
       <c r="B547">
-        <v>511</v>
+        <v>224</v>
       </c>
     </row>
     <row r="548" spans="1:2" x14ac:dyDescent="0.25">
@@ -4802,7 +4835,7 @@
         <v>9</v>
       </c>
       <c r="B548">
-        <v>530</v>
+        <v>234</v>
       </c>
     </row>
     <row r="549" spans="1:2" x14ac:dyDescent="0.25">
@@ -4810,6 +4843,214 @@
         <v>9</v>
       </c>
       <c r="B549">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="550" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A550">
+        <v>9</v>
+      </c>
+      <c r="B550">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="551" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A551">
+        <v>9</v>
+      </c>
+      <c r="B551">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="552" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A552">
+        <v>9</v>
+      </c>
+      <c r="B552">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="553" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A553">
+        <v>9</v>
+      </c>
+      <c r="B553">
+        <v>319</v>
+      </c>
+    </row>
+    <row r="554" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A554">
+        <v>9</v>
+      </c>
+      <c r="B554">
+        <v>331</v>
+      </c>
+    </row>
+    <row r="555" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A555">
+        <v>9</v>
+      </c>
+      <c r="B555">
+        <v>349</v>
+      </c>
+    </row>
+    <row r="556" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A556">
+        <v>9</v>
+      </c>
+      <c r="B556">
+        <v>352</v>
+      </c>
+    </row>
+    <row r="557" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A557">
+        <v>9</v>
+      </c>
+      <c r="B557">
+        <v>383</v>
+      </c>
+    </row>
+    <row r="558" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A558">
+        <v>9</v>
+      </c>
+      <c r="B558">
+        <v>390</v>
+      </c>
+    </row>
+    <row r="559" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A559">
+        <v>9</v>
+      </c>
+      <c r="B559">
+        <v>398</v>
+      </c>
+    </row>
+    <row r="560" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A560">
+        <v>9</v>
+      </c>
+      <c r="B560">
+        <v>402</v>
+      </c>
+    </row>
+    <row r="561" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A561">
+        <v>9</v>
+      </c>
+      <c r="B561">
+        <v>409</v>
+      </c>
+    </row>
+    <row r="562" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A562">
+        <v>9</v>
+      </c>
+      <c r="B562">
+        <v>416</v>
+      </c>
+    </row>
+    <row r="563" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A563">
+        <v>9</v>
+      </c>
+      <c r="B563">
+        <v>430</v>
+      </c>
+    </row>
+    <row r="564" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A564">
+        <v>9</v>
+      </c>
+      <c r="B564">
+        <v>438</v>
+      </c>
+    </row>
+    <row r="565" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A565">
+        <v>9</v>
+      </c>
+      <c r="B565">
+        <v>441</v>
+      </c>
+    </row>
+    <row r="566" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A566">
+        <v>9</v>
+      </c>
+      <c r="B566">
+        <v>451</v>
+      </c>
+    </row>
+    <row r="567" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A567">
+        <v>9</v>
+      </c>
+      <c r="B567">
+        <v>452</v>
+      </c>
+    </row>
+    <row r="568" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A568">
+        <v>9</v>
+      </c>
+      <c r="B568">
+        <v>457</v>
+      </c>
+    </row>
+    <row r="569" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A569">
+        <v>9</v>
+      </c>
+      <c r="B569">
+        <v>479</v>
+      </c>
+    </row>
+    <row r="570" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A570">
+        <v>9</v>
+      </c>
+      <c r="B570">
+        <v>504</v>
+      </c>
+    </row>
+    <row r="571" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A571">
+        <v>9</v>
+      </c>
+      <c r="B571">
+        <v>510</v>
+      </c>
+    </row>
+    <row r="572" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A572">
+        <v>9</v>
+      </c>
+      <c r="B572">
+        <v>511</v>
+      </c>
+    </row>
+    <row r="573" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A573">
+        <v>9</v>
+      </c>
+      <c r="B573">
+        <v>530</v>
+      </c>
+    </row>
+    <row r="574" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A574">
+        <v>9</v>
+      </c>
+      <c r="B574">
+        <v>533</v>
+      </c>
+    </row>
+    <row r="575" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A575">
+        <v>9</v>
+      </c>
+      <c r="B575">
         <v>544</v>
       </c>
     </row>
